--- a/Fase 1/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
+++ b/Fase 1/Evidencias Grupales/PLANILLA DE EVALUACIÓN FASE 1.xlsx
@@ -1,72 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28318"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/ge_galan_profesor_duoc_cl/Documents/2024-2/Clases/CAPSTONE/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="610" documentId="8_{2EFDF332-31E9-4C74-A6B5-E695634C1C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91B80DAC-7CE7-4715-8162-B9D290CDE525}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="EVALUACION1" sheetId="1" r:id="rId1"/>
-    <sheet name="RUBRICA" sheetId="6" r:id="rId2"/>
-    <sheet name="ESCALA_IEP" sheetId="2" state="hidden" r:id="rId3"/>
-    <sheet name="ESCALA_PRESENTACION" sheetId="3" state="hidden" r:id="rId4"/>
-    <sheet name="ESCALA_TRAB_EQUIP" sheetId="4" state="hidden" r:id="rId5"/>
-    <sheet name="RELEVANCIA-PUNTAJE" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet state="visible" name="EVALUACION1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="RUBRICA" sheetId="2" r:id="rId5"/>
+    <sheet state="hidden" name="ESCALA_IEP" sheetId="3" r:id="rId6"/>
+    <sheet state="hidden" name="ESCALA_PRESENTACION" sheetId="4" r:id="rId7"/>
+    <sheet state="hidden" name="ESCALA_TRAB_EQUIP" sheetId="5" r:id="rId8"/>
+    <sheet state="hidden" name="RELEVANCIA-PUNTAJE" sheetId="6" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="MR_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
+    <definedName name="PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
+    <definedName name="PR_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
+    <definedName name="RE_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
+    <definedName name="TL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
+    <definedName name="RE_NL">'RELEVANCIA-PUNTAJE'!$E$4</definedName>
+    <definedName name="NL">'RELEVANCIA-PUNTAJE'!$E$2</definedName>
     <definedName name="CL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
+    <definedName name="MR_NL">'RELEVANCIA-PUNTAJE'!$E$3</definedName>
     <definedName name="L">'RELEVANCIA-PUNTAJE'!$C$2</definedName>
+    <definedName name="MR_ML">'RELEVANCIA-PUNTAJE'!$D$3</definedName>
+    <definedName name="MR">'RELEVANCIA-PUNTAJE'!$A$3</definedName>
+    <definedName name="PR_NL">'RELEVANCIA-PUNTAJE'!$E$5</definedName>
+    <definedName name="PR_ML">'RELEVANCIA-PUNTAJE'!$D$5</definedName>
+    <definedName name="MR_L">'RELEVANCIA-PUNTAJE'!$C$3</definedName>
+    <definedName name="MR_TL">'RELEVANCIA-PUNTAJE'!$B$3</definedName>
     <definedName name="ML">'RELEVANCIA-PUNTAJE'!$D$2</definedName>
-    <definedName name="MR">'RELEVANCIA-PUNTAJE'!$A$3</definedName>
+    <definedName name="PR">'RELEVANCIA-PUNTAJE'!$A$5</definedName>
     <definedName name="MR_CL">'RELEVANCIA-PUNTAJE'!$B$3</definedName>
-    <definedName name="MR_L">'RELEVANCIA-PUNTAJE'!$C$3</definedName>
-    <definedName name="MR_ML">'RELEVANCIA-PUNTAJE'!$D$3</definedName>
-    <definedName name="MR_NL">'RELEVANCIA-PUNTAJE'!$E$3</definedName>
-    <definedName name="MR_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
-    <definedName name="MR_TL">'RELEVANCIA-PUNTAJE'!$B$3</definedName>
-    <definedName name="NL">'RELEVANCIA-PUNTAJE'!$E$2</definedName>
-    <definedName name="PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
-    <definedName name="PR">'RELEVANCIA-PUNTAJE'!$A$5</definedName>
-    <definedName name="PR_ML">'RELEVANCIA-PUNTAJE'!$D$5</definedName>
-    <definedName name="PR_NL">'RELEVANCIA-PUNTAJE'!$E$5</definedName>
-    <definedName name="PR_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
     <definedName name="PR_TL">'RELEVANCIA-PUNTAJE'!$B$5</definedName>
     <definedName name="RE">'RELEVANCIA-PUNTAJE'!$A$4</definedName>
     <definedName name="RE_ML">'RELEVANCIA-PUNTAJE'!$D$4</definedName>
-    <definedName name="RE_NL">'RELEVANCIA-PUNTAJE'!$E$4</definedName>
-    <definedName name="RE_PL">'RELEVANCIA-PUNTAJE'!#REF!</definedName>
     <definedName name="RE_TL">'RELEVANCIA-PUNTAJE'!$B$4</definedName>
-    <definedName name="TL">'RELEVANCIA-PUNTAJE'!$B$2</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="KXUBRvul/HNeBJ6TUfvAIbNs1Npm9uBh5PI3sTR84vY="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="106">
   <si>
     <t>INTEGRANTES</t>
   </si>
@@ -77,6 +56,15 @@
     <t>EMPLEAB</t>
   </si>
   <si>
+    <t>JAVIER FUENZALIDA</t>
+  </si>
+  <si>
+    <t>CAMILO ROMERO</t>
+  </si>
+  <si>
+    <t>TOMAS SAAVEDRA</t>
+  </si>
+  <si>
     <t>GRUPAL</t>
   </si>
   <si>
@@ -84,6 +72,9 @@
   </si>
   <si>
     <t>NIVELES DE LOGRO Y PUNTAJES</t>
+  </si>
+  <si>
+    <t>Contexto No es la Solución</t>
   </si>
   <si>
     <t>Aspectos a Evaluar</t>
@@ -99,6 +90,24 @@
   </si>
   <si>
     <t>No logrado</t>
+  </si>
+  <si>
+    <t>Presentar bien la problematica</t>
+  </si>
+  <si>
+    <t>no es claro el modelo de negocio</t>
+  </si>
+  <si>
+    <t>desordenada, no hay indice</t>
+  </si>
+  <si>
+    <t>arquitectura</t>
+  </si>
+  <si>
+    <t>Mapa Tecnologico?</t>
+  </si>
+  <si>
+    <t>Competencias??</t>
   </si>
   <si>
     <t>Puntaje</t>
@@ -122,6 +131,9 @@
     <t>PUNTAJE</t>
   </si>
   <si>
+    <t>Tranquilidad en la presentacion</t>
+  </si>
+  <si>
     <t>Indicador de Evaluación</t>
   </si>
   <si>
@@ -132,30 +144,40 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="11.0"/>
+      </rPr>
       <t>Completamente Logrado (</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
         <b/>
-        <sz val="10"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <sz val="10.0"/>
       </rPr>
       <t>100%)</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <rFont val="Calibri"/>
+        <b/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="11.0"/>
+      </rPr>
       <t>Logrado</t>
     </r>
     <r>
       <rPr>
+        <rFont val="Calibri"/>
         <b/>
-        <sz val="10"/>
         <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
+        <sz val="10.0"/>
       </rPr>
       <t xml:space="preserve">  (60%)</t>
     </r>
@@ -383,98 +405,92 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font/>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="20"/>
+      <sz val="20.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="9.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="16.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF3B3838"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -482,7 +498,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -498,14 +514,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9D9D9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <fgColor rgb="FFFEF2CB"/>
+        <bgColor rgb="FFFEF2CB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEF2CB"/>
-        <bgColor rgb="FFFEF2CB"/>
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -523,18 +539,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF262626"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF262626"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="33">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="35">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -548,7 +558,66 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
     </border>
     <border>
       <left style="thin">
@@ -561,33 +630,147 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="thin">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
+      </top>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+    </border>
+    <border>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF7F7F7F"/>
+      </top>
     </border>
     <border>
       <left style="medium">
@@ -599,8 +782,6 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -611,7 +792,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -620,7 +800,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -631,7 +810,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -640,11 +818,9 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -655,7 +831,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -664,7 +839,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -675,444 +849,215 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
+      <right style="medium">
         <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
+      </right>
+      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="79">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+  <cellXfs count="78">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="255" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="2" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="4" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="8" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="6" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf borderId="2" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="6" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="164" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="2" fillId="7" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="255" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf borderId="9" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="11" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="14" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="15" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="17" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="19" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="15" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="20" fillId="8" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="20" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="21" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="22" fillId="8" fontId="12" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="21" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="15" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="25" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="19" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="16" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="14" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf borderId="26" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf borderId="27" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="28" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="29" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf borderId="30" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="31" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="32" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf borderId="33" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf borderId="30" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf borderId="34" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1120,43 +1065,51 @@
       <fill>
         <patternFill patternType="none"/>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
+      <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Sheets">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4472C4"/>
@@ -1180,113 +1133,19 @@
         <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="0563C1"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1427,1384 +1286,1670 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K929"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="66.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="7" width="11.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
-    <col min="12" max="24" width="10.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.71"/>
+    <col customWidth="1" min="2" max="2" width="66.86"/>
+    <col customWidth="1" min="3" max="3" width="22.0"/>
+    <col customWidth="1" min="4" max="4" width="11.29"/>
+    <col customWidth="1" min="5" max="7" width="11.71"/>
+    <col customWidth="1" min="8" max="8" width="7.71"/>
+    <col customWidth="1" min="9" max="9" width="11.71"/>
+    <col customWidth="1" min="10" max="10" width="7.71"/>
+    <col customWidth="1" min="11" max="11" width="11.71"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" ht="14.45">
-      <c r="C2" s="2">
+    <row r="2">
+      <c r="C2" s="1">
         <v>0.75</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>0.25</v>
       </c>
-      <c r="E2" s="50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="14.45">
+      <c r="E2" s="2">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="64"/>
-    </row>
-    <row r="4" spans="1:11" ht="14.45">
-      <c r="A4" s="5">
-        <v>1</v>
-      </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="6">
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="8">
         <f>EVALUACION1!$C$24</f>
+        <v>6.6</v>
+      </c>
+      <c r="D4" s="8">
+        <f>$C$35</f>
+        <v>6</v>
+      </c>
+      <c r="E4" s="9">
+        <f t="shared" ref="E4:E7" si="1">C4*C$2+D4*D$2</f>
+        <v>6.45</v>
+      </c>
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="8">
+        <f>EVALUACION1!$C$24</f>
+        <v>6.6</v>
+      </c>
+      <c r="D5" s="8">
+        <f>C47</f>
+        <v>6</v>
+      </c>
+      <c r="E5" s="9">
+        <f t="shared" si="1"/>
+        <v>6.45</v>
+      </c>
+      <c r="G5" s="10"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="8">
+        <f>EVALUACION1!$C$24</f>
+        <v>6.6</v>
+      </c>
+      <c r="D6" s="8">
+        <f>C58</f>
+        <v>6</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" si="1"/>
+        <v>6.45</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11">
+        <v>4.0</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="8">
+        <f>EVALUACION1!$C$24</f>
+        <v>6.6</v>
+      </c>
+      <c r="D7" s="8">
+        <f>C69</f>
         <v>7</v>
       </c>
-      <c r="D4" s="6">
-        <f>$C$35</f>
+      <c r="E7" s="9">
+        <f t="shared" si="1"/>
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="43">
-        <f>C4*C$2+D4*D$2</f>
-        <v>7</v>
-      </c>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="14.45">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="6">
-        <f>EVALUACION1!$C$24</f>
-        <v>7</v>
-      </c>
-      <c r="D5" s="6">
-        <f>C47</f>
-        <v>7</v>
-      </c>
-      <c r="E5" s="43">
-        <f t="shared" ref="E5:E6" si="0">C5*C$2+D5*D$2</f>
-        <v>7</v>
-      </c>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="14.45">
-      <c r="A6" s="5">
-        <v>3</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="6">
-        <f>EVALUACION1!$C$24</f>
-        <v>7</v>
-      </c>
-      <c r="D6" s="6">
-        <f>C58</f>
-        <v>7</v>
-      </c>
-      <c r="E6" s="43">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="18" outlineLevel="1">
-      <c r="A11" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="65"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
-      <c r="I11" s="65"/>
-      <c r="J11" s="65"/>
-      <c r="K11" s="66"/>
-    </row>
-    <row r="12" spans="1:11" ht="14.45" outlineLevel="1">
-      <c r="A12" s="67"/>
-      <c r="B12" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="64"/>
-      <c r="D12" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="66"/>
-      <c r="F12" s="48" t="s">
+      <c r="D11" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="66"/>
-      <c r="H12" s="48" t="s">
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17"/>
+      <c r="M11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="66"/>
-      <c r="J12" s="48" t="s">
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K12" s="66"/>
-    </row>
-    <row r="13" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A13" s="68"/>
-      <c r="B13" s="35" t="str">
+      <c r="C12" s="5"/>
+      <c r="D12" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I12" s="17"/>
+      <c r="J12" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="17"/>
+      <c r="M12" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="18"/>
+      <c r="B13" s="20" t="str">
         <f>RUBRICA!A5</f>
         <v>1. Describe brevemente en qué consiste el Proyecto APT, justificando su relevancia para el campo laboral de su carrera.</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="16" t="str">
-        <f t="shared" ref="D13:D17" si="1">IF($C13=CL,"X","")</f>
+      <c r="C13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="22" t="str">
+        <f>IF($C13=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="22">
         <f>IF(D13="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F13" s="16" t="str">
-        <f t="shared" ref="F13:F17" si="2">IF($C13=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G13" s="16" t="str">
+      <c r="F13" s="22" t="str">
+        <f>IF($C13=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G13" s="22" t="str">
         <f>IF(F13="X",60*0.1,"")</f>
         <v/>
       </c>
-      <c r="H13" s="16" t="str">
-        <f t="shared" ref="H13:H17" si="3">IF($C13=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I13" s="16" t="str">
+      <c r="H13" s="22" t="str">
+        <f>IF($C13=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I13" s="22" t="str">
         <f>IF(H13="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16" t="str">
-        <f t="shared" ref="J13:J17" si="4">IF($C13=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K13" s="16" t="str">
-        <f t="shared" ref="K13:K17" si="5">IF($J13="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="26.45" customHeight="1" outlineLevel="1">
-      <c r="A14" s="68"/>
-      <c r="B14" s="35" t="str">
+      <c r="J13" s="22" t="str">
+        <f>IF($C13=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K13" s="22" t="str">
+        <f t="shared" ref="K13:K22" si="2">IF($J13="X",0,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" ht="26.25" customHeight="1" outlineLevel="1">
+      <c r="A14" s="18"/>
+      <c r="B14" s="20" t="str">
         <f>RUBRICA!A6</f>
         <v>2. Relaciona el Proyecto APT con las competencias del perfil de egreso de su Plan de Estudio.</v>
       </c>
-      <c r="C14" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="C14" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="22" t="str">
+        <f>IF($C14=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E14" s="16">
-        <f t="shared" ref="E14" si="6">IF(D14="X",100*0.05,"")</f>
+      <c r="E14" s="22">
+        <f t="shared" ref="E14:E16" si="3">IF(D14="X",100*0.05,"")</f>
         <v>5</v>
       </c>
-      <c r="F14" s="16" t="str">
+      <c r="F14" s="22" t="str">
+        <f>IF($C14=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G14" s="22" t="str">
+        <f t="shared" ref="G14:G16" si="4">IF(F14="X",60*0.05,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="22" t="str">
+        <f>IF($C14=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I14" s="22" t="str">
+        <f t="shared" ref="I14:I16" si="5">IF(H14="X",30*0.05,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="22" t="str">
+        <f>IF($C14=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K14" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G14" s="16" t="str">
-        <f t="shared" ref="G14" si="7">IF(F14="X",60*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="16" t="str">
+      <c r="M14" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" outlineLevel="1">
+      <c r="A15" s="18"/>
+      <c r="B15" s="20" t="str">
+        <f>RUBRICA!A8</f>
+        <v>4.  Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura. </v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="22" t="str">
+        <f>IF($C15=CL,"X","")</f>
+        <v>X</v>
+      </c>
+      <c r="E15" s="22">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I14" s="16" t="str">
-        <f t="shared" ref="I14" si="8">IF(H14="X",30*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="16" t="str">
+        <v>5</v>
+      </c>
+      <c r="F15" s="22" t="str">
+        <f>IF($C15=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G15" s="22" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K14" s="16" t="str">
+      <c r="H15" s="22" t="str">
+        <f>IF($C15=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I15" s="22" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="14.45" outlineLevel="1">
-      <c r="A15" s="68"/>
-      <c r="B15" s="35" t="str">
-        <f>RUBRICA!A8</f>
-        <v xml:space="preserve">4.  Argumenta por qué el proyecto es factible de realizarse en el marco de la asignatura. </v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="16" t="str">
-        <f t="shared" si="1"/>
+      <c r="J15" s="22" t="str">
+        <f>IF($C15=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K15" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1">
+      <c r="A16" s="18"/>
+      <c r="B16" s="20" t="str">
+        <f>RUBRICA!A9</f>
+        <v>5. Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar. </v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="22" t="str">
+        <f>IF($C16=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E15" s="16">
-        <f t="shared" ref="E15:E21" si="9">IF(D15="X",100*0.05,"")</f>
+      <c r="E16" s="22">
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="F15" s="16" t="str">
+      <c r="F16" s="22" t="str">
+        <f>IF($C16=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G16" s="22" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H16" s="22" t="str">
+        <f>IF($C16=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I16" s="22" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="J16" s="22" t="str">
+        <f>IF($C16=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K16" s="22" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="G15" s="16" t="str">
-        <f t="shared" ref="G15:G21" si="10">IF(F15="X",60*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I15" s="16" t="str">
-        <f t="shared" ref="I15:I21" si="11">IF(H15="X",30*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K15" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="14.45" outlineLevel="1">
-      <c r="A16" s="68"/>
-      <c r="B16" s="35" t="str">
-        <f>RUBRICA!A9</f>
-        <v xml:space="preserve">5. Formula objetivos claros, concisos y coherentes con la disciplina y la situación a abordar. </v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="16" t="str">
-        <f t="shared" si="1"/>
-        <v>X</v>
-      </c>
-      <c r="E16" s="16">
-        <f>IF(D16="X",100*0.05,"")</f>
-        <v>5</v>
-      </c>
-      <c r="F16" s="16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="G16" s="16" t="str">
-        <f>IF(F16="X",60*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="16" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="I16" s="16" t="str">
-        <f>IF(H16="X",30*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="16" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K16" s="16" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A17" s="68"/>
-      <c r="B17" s="35" t="str">
+      <c r="M16" s="11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1">
+      <c r="A17" s="18"/>
+      <c r="B17" s="20" t="str">
         <f>RUBRICA!A10</f>
         <v>6. Propone una metodología de trabajo que permite alcanzar los objetivos propuestos y es pertinente con los requerimientos disciplinares.</v>
       </c>
-      <c r="C17" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="16" t="str">
+      <c r="C17" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="22" t="str">
         <f>IF($C17=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E17" s="16">
-        <f t="shared" ref="E17" si="12">IF(D17="X",100*0.1,"")</f>
+      <c r="E17" s="22">
+        <f t="shared" ref="E17:E18" si="6">IF(D17="X",100*0.1,"")</f>
         <v>10</v>
       </c>
-      <c r="F17" s="16" t="str">
+      <c r="F17" s="22" t="str">
         <f>IF($C17=L,"X","")</f>
         <v/>
       </c>
-      <c r="G17" s="16" t="str">
-        <f t="shared" ref="G17" si="13">IF(F17="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="16" t="str">
+      <c r="G17" s="22" t="str">
+        <f t="shared" ref="G17:G18" si="7">IF(F17="X",60*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="22" t="str">
         <f>IF($C17=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I17" s="16" t="str">
-        <f t="shared" ref="I17" si="14">IF(H17="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="16" t="str">
+      <c r="I17" s="22" t="str">
+        <f t="shared" ref="I17:I18" si="8">IF(H17="X",30*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="22" t="str">
         <f>IF($C17=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K17" s="16" t="str">
-        <f t="shared" ref="K17:K22" si="15">IF($J17="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A18" s="68"/>
-      <c r="B18" s="35" t="str">
+      <c r="K17" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" outlineLevel="1">
+      <c r="A18" s="18"/>
+      <c r="B18" s="20" t="str">
         <f>RUBRICA!A11</f>
-        <v xml:space="preserve">7. Establece un plan de trabajo para su proyecto APT considerando los recursos, duración, facilitadores y obstaculizadores en el desarrollo de las actividades. </v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="16" t="str">
+        <v>7. Establece un plan de trabajo para su proyecto APT considerando los recursos, duración, facilitadores y obstaculizadores en el desarrollo de las actividades. </v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="22" t="str">
         <f>IF($C18=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E18" s="16">
-        <f t="shared" ref="E18:E19" si="16">IF(D18="X",100*0.1,"")</f>
+      <c r="E18" s="22">
+        <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="F18" s="16" t="str">
+      <c r="F18" s="22" t="str">
         <f>IF($C18=L,"X","")</f>
         <v/>
       </c>
-      <c r="G18" s="16" t="str">
-        <f t="shared" ref="G18:G19" si="17">IF(F18="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="16" t="str">
+      <c r="G18" s="22" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="H18" s="22" t="str">
         <f>IF($C18=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I18" s="16" t="str">
-        <f t="shared" ref="I18:I19" si="18">IF(H18="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="16" t="str">
+      <c r="I18" s="22" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="J18" s="22" t="str">
         <f>IF($C18=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K18" s="16" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A19" s="68"/>
-      <c r="B19" s="35" t="str">
+      <c r="K18" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" outlineLevel="1">
+      <c r="A19" s="18"/>
+      <c r="B19" s="20" t="str">
         <f>RUBRICA!A12</f>
         <v>8. Determina evidencias, justificando cómo estas dan cuenta del logro de las actividades del Proyecto APT.</v>
       </c>
-      <c r="C19" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="16" t="str">
+      <c r="C19" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="22" t="str">
         <f>IF($C19=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E19" s="16">
-        <f>IF(D19="X",100*0.05,"")</f>
+      <c r="E19" s="22">
+        <f t="shared" ref="E19:E21" si="9">IF(D19="X",100*0.05,"")</f>
         <v>5</v>
       </c>
-      <c r="F19" s="16" t="str">
+      <c r="F19" s="22" t="str">
         <f>IF($C19=L,"X","")</f>
         <v/>
       </c>
-      <c r="G19" s="16" t="str">
-        <f t="shared" ref="G19" si="19">IF(F19="X",60*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="16" t="str">
+      <c r="G19" s="22" t="str">
+        <f t="shared" ref="G19:G21" si="10">IF(F19="X",60*0.05,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="22" t="str">
         <f>IF($C19=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I19" s="16" t="str">
-        <f t="shared" ref="I19" si="20">IF(H19="X",30*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="16" t="str">
+      <c r="I19" s="22" t="str">
+        <f t="shared" ref="I19:I21" si="11">IF(H19="X",30*0.05,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="22" t="str">
         <f>IF($C19=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K19" s="16" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A20" s="68"/>
-      <c r="B20" s="35" t="str">
+      <c r="K19" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" outlineLevel="1">
+      <c r="A20" s="18"/>
+      <c r="B20" s="20" t="str">
         <f>RUBRICA!A13</f>
-        <v xml:space="preserve">9. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="16" t="str">
+        <v>9. Utiliza reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="22" t="str">
         <f>IF($C20=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E20" s="16">
-        <f>IF(D20="X",100*0.05,"")</f>
+      <c r="E20" s="22">
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="F20" s="16" t="str">
+      <c r="F20" s="22" t="str">
         <f>IF($C20=L,"X","")</f>
         <v/>
       </c>
-      <c r="G20" s="16" t="str">
+      <c r="G20" s="22" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="H20" s="16" t="str">
+      <c r="H20" s="22" t="str">
         <f>IF($C20=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I20" s="16" t="str">
+      <c r="I20" s="22" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J20" s="16" t="str">
+      <c r="J20" s="22" t="str">
         <f>IF($C20=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K20" s="16" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="22.9" customHeight="1" outlineLevel="1">
-      <c r="A21" s="68"/>
-      <c r="B21" s="35" t="str">
+      <c r="K20" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1" outlineLevel="1">
+      <c r="A21" s="18"/>
+      <c r="B21" s="20" t="str">
         <f>RUBRICA!A14</f>
         <v>10. Cumple completando el contenido del informe de presentación del proyecto de acuerdo con la plantilla entregada.</v>
       </c>
-      <c r="C21" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="16" t="str">
+      <c r="C21" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="22" t="str">
         <f>IF($C21=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="22">
         <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="F21" s="16" t="str">
+      <c r="F21" s="22" t="str">
         <f>IF($C21=L,"X","")</f>
         <v/>
       </c>
-      <c r="G21" s="16" t="str">
+      <c r="G21" s="22" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="H21" s="16" t="str">
+      <c r="H21" s="22" t="str">
         <f>IF($C21=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I21" s="16" t="str">
+      <c r="I21" s="22" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="J21" s="16" t="str">
+      <c r="J21" s="22" t="str">
         <f>IF($C21=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K21" s="16" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="24" outlineLevel="1">
-      <c r="A22" s="68"/>
-      <c r="B22" s="35" t="str">
+      <c r="K21" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="36.75" customHeight="1" outlineLevel="1">
+      <c r="A22" s="18"/>
+      <c r="B22" s="20" t="str">
         <f>RUBRICA!A16</f>
         <v>12. Desarrolla un plan de trabajo que permita del logro de los objetivos propuestos del proyecto de 
 acuerdo a los tiempos para su desarrollo</v>
       </c>
-      <c r="C22" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="16" t="str">
+      <c r="C22" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="22" t="str">
         <f>IF($C22=CL,"X","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="22" t="str">
+        <f>IF(D22="X",100*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="22" t="str">
+        <f>IF($C22=L,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E22" s="16">
-        <f>IF(D22="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F22" s="16" t="str">
-        <f>IF($C22=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G22" s="16" t="str">
+      <c r="G22" s="22">
         <f>IF(F22="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="16" t="str">
+        <v>6</v>
+      </c>
+      <c r="H22" s="22" t="str">
         <f>IF($C22=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I22" s="16" t="str">
+      <c r="I22" s="22" t="str">
         <f>IF(H22="X",30*0.1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16" t="str">
+      <c r="J22" s="22" t="str">
         <f>IF($C22=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K22" s="16" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A23" s="67"/>
-      <c r="B23" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="37">
+      <c r="K22" s="22" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" outlineLevel="1">
+      <c r="A23" s="18"/>
+      <c r="B23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="25">
         <f>E23+G23+I23+K23</f>
-        <v>70</v>
-      </c>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19">
+        <v>66</v>
+      </c>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26">
         <f>SUM(E13:E22)</f>
-        <v>70</v>
-      </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19">
+        <v>60</v>
+      </c>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26">
         <f>SUM(G13:G22)</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19">
+        <v>6</v>
+      </c>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26">
         <f>SUM(I13:I22)</f>
         <v>0</v>
       </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19">
+      <c r="J23" s="26"/>
+      <c r="K23" s="26">
         <f>SUM(K13:K22)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1">
-      <c r="A24" s="64"/>
-      <c r="B24" s="36" t="s">
+    <row r="24" ht="15.75" customHeight="1" outlineLevel="1">
+      <c r="A24" s="5"/>
+      <c r="B24" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="28">
+        <f>VLOOKUP(C23,ESCALA_IEP!A2:B142,2,FALSE)</f>
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="31" t="str">
+        <f>$B$4</f>
+        <v>JAVIER FUENZALIDA</v>
+      </c>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="33"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="18"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="34"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="36"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="18"/>
+      <c r="B29" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="18"/>
+      <c r="B30" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="20">
-        <f>VLOOKUP(C23,ESCALA_IEP!A2:B142,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A27" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="45" t="s">
+      <c r="G30" s="17"/>
+      <c r="H30" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I30" s="17"/>
+      <c r="J30" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="46">
-        <f>$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="D27" s="69"/>
-      <c r="E27" s="69"/>
-      <c r="F27" s="69"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="70"/>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A28" s="67"/>
-      <c r="B28" s="64"/>
-      <c r="C28" s="71"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="72"/>
-      <c r="H28" s="72"/>
-      <c r="I28" s="72"/>
-      <c r="J28" s="72"/>
-      <c r="K28" s="73"/>
-    </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A29" s="67"/>
-      <c r="B29" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="66"/>
-    </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A30" s="67"/>
-      <c r="B30" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="66"/>
-      <c r="F30" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="G30" s="66"/>
-      <c r="H30" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="66"/>
-      <c r="J30" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="K30" s="66"/>
-    </row>
-    <row r="31" spans="1:11" ht="24.6" customHeight="1">
-      <c r="A31" s="67"/>
-      <c r="B31" s="35" t="str">
+      <c r="K30" s="17"/>
+    </row>
+    <row r="31" ht="24.0" customHeight="1">
+      <c r="A31" s="18"/>
+      <c r="B31" s="20" t="str">
         <f>RUBRICA!A7</f>
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
       </c>
-      <c r="C31" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="16" t="str">
-        <f t="shared" ref="D31:D32" si="21">IF($C31=CL,"X","")</f>
+      <c r="C31" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="22" t="str">
+        <f>IF($C31=CL,"X","")</f>
+        <v/>
+      </c>
+      <c r="E31" s="22" t="str">
+        <f t="shared" ref="E31:E33" si="12">IF(D31="X",100*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="22" t="str">
+        <f>IF($C31=L,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E31" s="16">
-        <f>IF(D31="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F31" s="16" t="str">
-        <f t="shared" ref="F31:F32" si="22">IF($C31=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G31" s="16" t="str">
-        <f>IF(F31="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="16" t="str">
-        <f t="shared" ref="H31:H32" si="23">IF($C31=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I31" s="16" t="str">
-        <f>IF(H31="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="16" t="str">
-        <f t="shared" ref="J31:J32" si="24">IF($C31=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K31" s="16" t="str">
-        <f t="shared" ref="K31:K32" si="25">IF($J31="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="25.9" customHeight="1">
-      <c r="A32" s="67"/>
-      <c r="B32" s="35" t="str">
+      <c r="G31" s="22">
+        <f t="shared" ref="G31:G33" si="13">IF(F31="X",60*0.1,"")</f>
+        <v>6</v>
+      </c>
+      <c r="H31" s="22" t="str">
+        <f>IF($C31=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I31" s="22" t="str">
+        <f t="shared" ref="I31:I33" si="14">IF(H31="X",30*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="22" t="str">
+        <f>IF($C31=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K31" s="22" t="str">
+        <f t="shared" ref="K31:K33" si="15">IF($J31="X",0,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="25.5" customHeight="1">
+      <c r="A32" s="18"/>
+      <c r="B32" s="20" t="str">
         <f>RUBRICA!A15</f>
         <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
       </c>
-      <c r="C32" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="16" t="str">
-        <f t="shared" si="21"/>
+      <c r="C32" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="22" t="str">
+        <f>IF($C32=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E32" s="16">
-        <f>IF(D32="X",100*0.1,"")</f>
+      <c r="E32" s="22">
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="F32" s="16" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="G32" s="16" t="str">
-        <f>IF(F32="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="16" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="I32" s="16" t="str">
-        <f>IF(H32="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="16" t="str">
-        <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="K32" s="16" t="str">
-        <f t="shared" si="25"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="14.45">
-      <c r="A33" s="67"/>
-      <c r="B33" s="35" t="str">
+      <c r="F32" s="22" t="str">
+        <f>IF($C32=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G32" s="22" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="H32" s="22" t="str">
+        <f>IF($C32=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I32" s="22" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J32" s="22" t="str">
+        <f>IF($C32=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K32" s="22" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="18"/>
+      <c r="B33" s="20" t="str">
         <f>RUBRICA!A17</f>
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
-      <c r="C33" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="16" t="str">
+      <c r="C33" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="22" t="str">
         <f>IF($C33=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E33" s="16">
-        <f>IF(D33="X",100*0.1,"")</f>
+      <c r="E33" s="22">
+        <f t="shared" si="12"/>
         <v>10</v>
       </c>
-      <c r="F33" s="16" t="str">
+      <c r="F33" s="22" t="str">
         <f>IF($C33=L,"X","")</f>
         <v/>
       </c>
-      <c r="G33" s="16" t="str">
-        <f>IF(F33="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="16" t="str">
+      <c r="G33" s="22" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="H33" s="22" t="str">
         <f>IF($C33=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I33" s="16" t="str">
-        <f>IF(H33="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="16" t="str">
+      <c r="I33" s="22" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J33" s="22" t="str">
         <f>IF($C33=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K33" s="16" t="str">
-        <f>IF($J33="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A34" s="67"/>
-      <c r="B34" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="18">
+      <c r="K33" s="22" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="18"/>
+      <c r="B34" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="39">
         <f>E34+G34+I34+K34</f>
-        <v>30</v>
-      </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19">
+        <v>26</v>
+      </c>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26">
         <f>SUM(E31:E33)</f>
-        <v>30</v>
-      </c>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19">
-        <f t="shared" ref="G34:K34" si="26">SUM(G31:G33)</f>
+        <v>20</v>
+      </c>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26">
+        <f>SUM(G31:G33)</f>
+        <v>6</v>
+      </c>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26">
+        <f>SUM(I31:I33)</f>
         <v>0</v>
       </c>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19">
-        <f t="shared" si="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26">
+        <f>SUM(K31:K33)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A35" s="64"/>
-      <c r="B35" s="17" t="s">
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="5"/>
+      <c r="B35" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="28">
+        <f>VLOOKUP(C34,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="B36" s="41"/>
+      <c r="C36" s="42"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="B37" s="41"/>
+      <c r="C37" s="42"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="31" t="str">
+        <f>B5</f>
+        <v>CAMILO ROMERO</v>
+      </c>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="33"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="18"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="36"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="18"/>
+      <c r="B41" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="18"/>
+      <c r="B42" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="17"/>
+      <c r="F42" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C35" s="20">
-        <f>VLOOKUP(C34,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B36" s="22"/>
-      <c r="C36" s="23"/>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B37" s="22"/>
-      <c r="C37" s="23"/>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A39" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="45" t="s">
+      <c r="G42" s="17"/>
+      <c r="H42" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I42" s="17"/>
+      <c r="J42" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C39" s="46">
-        <f>B5</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="69"/>
-      <c r="E39" s="69"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="69"/>
-      <c r="K39" s="70"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A40" s="67"/>
-      <c r="B40" s="64"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="72"/>
-      <c r="F40" s="72"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="72"/>
-      <c r="I40" s="72"/>
-      <c r="J40" s="72"/>
-      <c r="K40" s="73"/>
-    </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A41" s="67"/>
-      <c r="B41" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="66"/>
-    </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A42" s="67"/>
-      <c r="B42" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="64"/>
-      <c r="D42" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="66"/>
-      <c r="F42" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="66"/>
-      <c r="H42" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="66"/>
-      <c r="J42" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="K42" s="66"/>
-    </row>
-    <row r="43" spans="1:11" ht="25.9" customHeight="1">
-      <c r="A43" s="67"/>
-      <c r="B43" s="35" t="str">
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" ht="25.5" customHeight="1">
+      <c r="A43" s="18"/>
+      <c r="B43" s="20" t="str">
         <f>RUBRICA!A7</f>
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
       </c>
-      <c r="C43" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="16" t="str">
-        <f t="shared" ref="D43:D44" si="27">IF($C43=CL,"X","")</f>
+      <c r="C43" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="22" t="str">
+        <f>IF($C43=CL,"X","")</f>
+        <v/>
+      </c>
+      <c r="E43" s="22" t="str">
+        <f t="shared" ref="E43:E45" si="16">IF(D43="X",100*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="22" t="str">
+        <f>IF($C43=L,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E43" s="16">
-        <f>IF(D43="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F43" s="16" t="str">
-        <f t="shared" ref="F43:F44" si="28">IF($C43=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G43" s="16" t="str">
-        <f>IF(F43="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="16" t="str">
-        <f t="shared" ref="H43:H44" si="29">IF($C43=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I43" s="16" t="str">
-        <f>IF(H43="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J43" s="16" t="str">
-        <f t="shared" ref="J43:J44" si="30">IF($C43=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K43" s="16" t="str">
-        <f t="shared" ref="K43:K44" si="31">IF($J43="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="24">
-      <c r="A44" s="67"/>
-      <c r="B44" s="35" t="str">
+      <c r="G43" s="22">
+        <f t="shared" ref="G43:G45" si="17">IF(F43="X",60*0.1,"")</f>
+        <v>6</v>
+      </c>
+      <c r="H43" s="22" t="str">
+        <f>IF($C43=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I43" s="22" t="str">
+        <f t="shared" ref="I43:I45" si="18">IF(H43="X",30*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="22" t="str">
+        <f>IF($C43=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K43" s="22" t="str">
+        <f t="shared" ref="K43:K45" si="19">IF($J43="X",0,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="18"/>
+      <c r="B44" s="20" t="str">
         <f>RUBRICA!A15</f>
         <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
       </c>
-      <c r="C44" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="16" t="str">
-        <f t="shared" si="27"/>
+      <c r="C44" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="22" t="str">
+        <f>IF($C44=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E44" s="16">
-        <f>IF(D44="X",100*0.1,"")</f>
+      <c r="E44" s="22">
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
-      <c r="F44" s="16" t="str">
-        <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="G44" s="16" t="str">
-        <f>IF(F44="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="16" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="I44" s="16" t="str">
-        <f>IF(H44="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J44" s="16" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="K44" s="16" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A45" s="67"/>
-      <c r="B45" s="35" t="str">
+      <c r="F44" s="22" t="str">
+        <f>IF($C44=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G44" s="22" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="H44" s="22" t="str">
+        <f>IF($C44=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I44" s="22" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J44" s="22" t="str">
+        <f>IF($C44=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K44" s="22" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="18"/>
+      <c r="B45" s="20" t="str">
         <f>RUBRICA!A17</f>
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
-      <c r="C45" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="16" t="str">
+      <c r="C45" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="22" t="str">
         <f>IF($C45=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E45" s="16">
-        <f>IF(D45="X",100*0.1,"")</f>
+      <c r="E45" s="22">
+        <f t="shared" si="16"/>
         <v>10</v>
       </c>
-      <c r="F45" s="16" t="str">
+      <c r="F45" s="22" t="str">
         <f>IF($C45=L,"X","")</f>
         <v/>
       </c>
-      <c r="G45" s="16" t="str">
-        <f>IF(F45="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="16" t="str">
+      <c r="G45" s="22" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="H45" s="22" t="str">
         <f>IF($C45=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I45" s="16" t="str">
-        <f>IF(H45="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J45" s="16" t="str">
+      <c r="I45" s="22" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="J45" s="22" t="str">
         <f>IF($C45=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K45" s="16" t="str">
-        <f>IF($J45="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A46" s="67"/>
-      <c r="B46" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" s="18">
+      <c r="K45" s="22" t="str">
+        <f t="shared" si="19"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="18"/>
+      <c r="B46" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="39">
         <f>E46+G46+I46+K46</f>
-        <v>30</v>
-      </c>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19">
+        <v>26</v>
+      </c>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26">
         <f>SUM(E43:E45)</f>
-        <v>30</v>
-      </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19">
-        <f t="shared" ref="G46" si="32">SUM(G43:G45)</f>
+        <v>20</v>
+      </c>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26">
+        <f>SUM(G43:G45)</f>
+        <v>6</v>
+      </c>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26">
+        <f>SUM(I43:I45)</f>
         <v>0</v>
       </c>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19">
-        <f t="shared" ref="I46" si="33">SUM(I43:I45)</f>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26">
+        <f>SUM(K43:K45)</f>
         <v>0</v>
       </c>
-      <c r="J46" s="19"/>
-      <c r="K46" s="19">
-        <f t="shared" ref="K46" si="34">SUM(K43:K45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A47" s="64"/>
-      <c r="B47" s="17" t="s">
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="5"/>
+      <c r="B47" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="28">
+        <f>VLOOKUP(C46,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="B48" s="41"/>
+      <c r="C48" s="42"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="B49" s="41"/>
+      <c r="C49" s="42"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="31" t="str">
+        <f>B6</f>
+        <v>TOMAS SAAVEDRA</v>
+      </c>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="33"/>
+      <c r="M50" s="11" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="18"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="34"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="36"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="18"/>
+      <c r="B52" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="18"/>
+      <c r="B53" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="17"/>
+      <c r="F53" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C47" s="20">
-        <f>VLOOKUP(C46,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B48" s="22"/>
-      <c r="C48" s="23"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B49" s="22"/>
-      <c r="C49" s="23"/>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A50" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="B50" s="45" t="s">
+      <c r="G53" s="17"/>
+      <c r="H53" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I53" s="17"/>
+      <c r="J53" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="46">
-        <f>B6</f>
-        <v>0</v>
-      </c>
-      <c r="D50" s="69"/>
-      <c r="E50" s="69"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="69"/>
-      <c r="I50" s="69"/>
-      <c r="J50" s="69"/>
-      <c r="K50" s="70"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A51" s="67"/>
-      <c r="B51" s="64"/>
-      <c r="C51" s="71"/>
-      <c r="D51" s="72"/>
-      <c r="E51" s="72"/>
-      <c r="F51" s="72"/>
-      <c r="G51" s="72"/>
-      <c r="H51" s="72"/>
-      <c r="I51" s="72"/>
-      <c r="J51" s="72"/>
-      <c r="K51" s="73"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A52" s="67"/>
-      <c r="B52" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C52" s="47" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="65"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
-      <c r="J52" s="65"/>
-      <c r="K52" s="66"/>
-    </row>
-    <row r="53" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A53" s="67"/>
-      <c r="B53" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="64"/>
-      <c r="D53" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="E53" s="66"/>
-      <c r="F53" s="48" t="s">
-        <v>8</v>
-      </c>
-      <c r="G53" s="66"/>
-      <c r="H53" s="48" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" s="66"/>
-      <c r="J53" s="48" t="s">
-        <v>10</v>
-      </c>
-      <c r="K53" s="66"/>
-    </row>
-    <row r="54" spans="1:11" ht="25.9" customHeight="1">
-      <c r="A54" s="67"/>
-      <c r="B54" s="35" t="str">
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" ht="25.5" customHeight="1">
+      <c r="A54" s="18"/>
+      <c r="B54" s="20" t="str">
         <f>RUBRICA!A7</f>
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
       </c>
-      <c r="C54" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="16" t="str">
-        <f t="shared" ref="D54:D55" si="35">IF($C54=CL,"X","")</f>
+      <c r="C54" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="22" t="str">
+        <f>IF($C54=CL,"X","")</f>
+        <v/>
+      </c>
+      <c r="E54" s="22" t="str">
+        <f t="shared" ref="E54:E56" si="20">IF(D54="X",100*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="22" t="str">
+        <f>IF($C54=L,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E54" s="16">
-        <f>IF(D54="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F54" s="16" t="str">
-        <f t="shared" ref="F54:F55" si="36">IF($C54=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G54" s="16" t="str">
-        <f>IF(F54="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="16" t="str">
-        <f t="shared" ref="H54:H55" si="37">IF($C54=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I54" s="16" t="str">
-        <f>IF(H54="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="16" t="str">
-        <f t="shared" ref="J54:J55" si="38">IF($C54=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K54" s="16" t="str">
-        <f t="shared" ref="K54:K55" si="39">IF($J54="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="24">
-      <c r="A55" s="67"/>
-      <c r="B55" s="35" t="str">
+      <c r="G54" s="22">
+        <f t="shared" ref="G54:G56" si="21">IF(F54="X",60*0.1,"")</f>
+        <v>6</v>
+      </c>
+      <c r="H54" s="22" t="str">
+        <f>IF($C54=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I54" s="22" t="str">
+        <f t="shared" ref="I54:I56" si="22">IF(H54="X",30*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="22" t="str">
+        <f>IF($C54=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K54" s="22" t="str">
+        <f t="shared" ref="K54:K56" si="23">IF($J54="X",0,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="34.5" customHeight="1">
+      <c r="A55" s="18"/>
+      <c r="B55" s="20" t="str">
         <f>RUBRICA!A15</f>
         <v>11. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
       </c>
-      <c r="C55" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" s="16" t="str">
-        <f t="shared" si="35"/>
+      <c r="C55" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="22" t="str">
+        <f>IF($C55=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E55" s="16">
-        <f>IF(D55="X",100*0.1,"")</f>
+      <c r="E55" s="22">
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="F55" s="16" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="G55" s="16" t="str">
-        <f>IF(F55="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="16" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="I55" s="16" t="str">
-        <f>IF(H55="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="16" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K55" s="16" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A56" s="67"/>
-      <c r="B56" s="35" t="str">
+      <c r="F55" s="22" t="str">
+        <f>IF($C55=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G55" s="22" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="H55" s="22" t="str">
+        <f>IF($C55=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I55" s="22" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J55" s="22" t="str">
+        <f>IF($C55=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K55" s="22" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="18"/>
+      <c r="B56" s="20" t="str">
         <f>RUBRICA!A17</f>
         <v>13. Colaboración y trabajo en equipo *</v>
       </c>
-      <c r="C56" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="16" t="str">
+      <c r="C56" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="22" t="str">
         <f>IF($C56=CL,"X","")</f>
         <v>X</v>
       </c>
-      <c r="E56" s="16">
-        <f>IF(D56="X",100*0.1,"")</f>
+      <c r="E56" s="22">
+        <f t="shared" si="20"/>
         <v>10</v>
       </c>
-      <c r="F56" s="16" t="str">
+      <c r="F56" s="22" t="str">
         <f>IF($C56=L,"X","")</f>
         <v/>
       </c>
-      <c r="G56" s="16" t="str">
-        <f>IF(F56="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="16" t="str">
+      <c r="G56" s="22" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="H56" s="22" t="str">
         <f>IF($C56=ML,"X","")</f>
         <v/>
       </c>
-      <c r="I56" s="16" t="str">
-        <f>IF(H56="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J56" s="16" t="str">
+      <c r="I56" s="22" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J56" s="22" t="str">
         <f>IF($C56=NL,"X","")</f>
         <v/>
       </c>
-      <c r="K56" s="16" t="str">
-        <f>IF($J56="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A57" s="67"/>
-      <c r="B57" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="18">
+      <c r="K56" s="22" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="18"/>
+      <c r="B57" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C57" s="39">
         <f>E57+G57+I57+K57</f>
-        <v>30</v>
-      </c>
-      <c r="D57" s="19">
+        <v>26</v>
+      </c>
+      <c r="D57" s="26">
         <f>COUNTIF(D55:D56,"X")</f>
         <v>2</v>
       </c>
-      <c r="E57" s="19">
-        <f>SUM(E54:E56)</f>
+      <c r="E57" s="26">
+        <f t="shared" ref="E57:K57" si="24">SUM(E54:E56)</f>
+        <v>20</v>
+      </c>
+      <c r="F57" s="26">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="G57" s="26">
+        <f t="shared" si="24"/>
+        <v>6</v>
+      </c>
+      <c r="H57" s="26">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="I57" s="26">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="J57" s="26">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="26">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="5"/>
+      <c r="B58" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="28">
+        <f>VLOOKUP(C57,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="B59" s="41"/>
+      <c r="C59" s="42"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="31" t="str">
+        <f>B7</f>
+        <v/>
+      </c>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="33"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="18"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="36"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="18"/>
+      <c r="B63" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
+      <c r="G63" s="16"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="18"/>
+      <c r="B64" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="17"/>
+      <c r="F64" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" s="17"/>
+      <c r="H64" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I64" s="17"/>
+      <c r="J64" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" ht="25.5" customHeight="1">
+      <c r="A65" s="18"/>
+      <c r="B65" s="20" t="str">
+        <f>RUBRICA!A18</f>
+        <v>Total</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="22" t="str">
+        <f>IF($C65=CL,"X","")</f>
+        <v>X</v>
+      </c>
+      <c r="E65" s="22">
+        <f t="shared" ref="E65:E67" si="25">IF(D65="X",100*0.1,"")</f>
+        <v>10</v>
+      </c>
+      <c r="F65" s="22" t="str">
+        <f>IF($C65=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G65" s="22" t="str">
+        <f t="shared" ref="G65:G67" si="26">IF(F65="X",60*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="22" t="str">
+        <f>IF($C65=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I65" s="22" t="str">
+        <f t="shared" ref="I65:I67" si="27">IF(H65="X",30*0.1,"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="22" t="str">
+        <f>IF($C65=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K65" s="22" t="str">
+        <f t="shared" ref="K65:K67" si="28">IF($J65="X",0,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="18"/>
+      <c r="B66" s="20" t="str">
+        <f>RUBRICA!A26</f>
+        <v/>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="22" t="str">
+        <f>IF($C66=CL,"X","")</f>
+        <v>X</v>
+      </c>
+      <c r="E66" s="22">
+        <f t="shared" si="25"/>
+        <v>10</v>
+      </c>
+      <c r="F66" s="22" t="str">
+        <f>IF($C66=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G66" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="H66" s="22" t="str">
+        <f>IF($C66=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I66" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="J66" s="22" t="str">
+        <f>IF($C66=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K66" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="18"/>
+      <c r="B67" s="20" t="str">
+        <f>RUBRICA!A28</f>
+        <v/>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="22" t="str">
+        <f>IF($C67=CL,"X","")</f>
+        <v>X</v>
+      </c>
+      <c r="E67" s="22">
+        <f t="shared" si="25"/>
+        <v>10</v>
+      </c>
+      <c r="F67" s="22" t="str">
+        <f>IF($C67=L,"X","")</f>
+        <v/>
+      </c>
+      <c r="G67" s="22" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="H67" s="22" t="str">
+        <f>IF($C67=ML,"X","")</f>
+        <v/>
+      </c>
+      <c r="I67" s="22" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="J67" s="22" t="str">
+        <f>IF($C67=NL,"X","")</f>
+        <v/>
+      </c>
+      <c r="K67" s="22" t="str">
+        <f t="shared" si="28"/>
+        <v/>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="18"/>
+      <c r="B68" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="39">
+        <f>E68+G68+I68+K68</f>
         <v>30</v>
       </c>
-      <c r="F57" s="19">
-        <f t="shared" ref="F57" si="40">SUM(F54:F56)</f>
+      <c r="D68" s="26">
+        <f>COUNTIF(D66:D67,"X")</f>
+        <v>2</v>
+      </c>
+      <c r="E68" s="26">
+        <f t="shared" ref="E68:K68" si="29">SUM(E65:E67)</f>
+        <v>30</v>
+      </c>
+      <c r="F68" s="26">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="G57" s="19">
-        <f t="shared" ref="G57" si="41">SUM(G54:G56)</f>
+      <c r="G68" s="26">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H57" s="19">
-        <f t="shared" ref="H57" si="42">SUM(H54:H56)</f>
+      <c r="H68" s="26">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="I57" s="19">
-        <f t="shared" ref="I57" si="43">SUM(I54:I56)</f>
+      <c r="I68" s="26">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="J57" s="19">
-        <f t="shared" ref="J57" si="44">SUM(J54:J56)</f>
+      <c r="J68" s="26">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K57" s="19">
-        <f t="shared" ref="K57" si="45">SUM(K54:K56)</f>
+      <c r="K68" s="26">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A58" s="64"/>
-      <c r="B58" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C58" s="20">
-        <f>VLOOKUP(C57,ESCALA_TRAB_EQUIP!A2:B62,2,FALSE)</f>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="5"/>
+      <c r="B69" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="28">
+        <f>VLOOKUP(C68,ESCALA_TRAB_EQUIP!A13:B73,2,FALSE)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1">
-      <c r="B59" s="22"/>
-      <c r="C59" s="23"/>
-    </row>
-    <row r="60" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
     <row r="70" ht="15.75" customHeight="1"/>
     <row r="71" ht="15.75" customHeight="1"/>
     <row r="72" ht="15.75" customHeight="1"/>
@@ -3665,1561 +3810,2626 @@
     <row r="927" ht="15.75" customHeight="1"/>
     <row r="928" ht="15.75" customHeight="1"/>
     <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B50:B51"/>
+  <mergeCells count="44">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C41:C42"/>
     <mergeCell ref="C52:C53"/>
-    <mergeCell ref="C50:K51"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="A50:A58"/>
+    <mergeCell ref="C27:K28"/>
+    <mergeCell ref="D29:K29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
     <mergeCell ref="H30:I30"/>
     <mergeCell ref="J30:K30"/>
-    <mergeCell ref="D52:K52"/>
+    <mergeCell ref="C39:K40"/>
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="F53:G53"/>
     <mergeCell ref="H53:I53"/>
-    <mergeCell ref="A39:A47"/>
-    <mergeCell ref="A27:A35"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="A11:A24"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:K28"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="D29:K29"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="C39:K40"/>
-    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="J53:K53"/>
     <mergeCell ref="D41:K41"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="F42:G42"/>
     <mergeCell ref="H42:I42"/>
     <mergeCell ref="J42:K42"/>
+    <mergeCell ref="C50:K51"/>
+    <mergeCell ref="D52:K52"/>
+    <mergeCell ref="A11:A24"/>
+    <mergeCell ref="A27:A35"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A39:A47"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="A50:A58"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="A61:A69"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:K62"/>
+    <mergeCell ref="C63:C64"/>
+    <mergeCell ref="D63:K63"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:E6">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+  <conditionalFormatting sqref="C4:E7">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>4</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4:E7">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E6" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>1</formula1>
-      <formula2>7</formula2>
+  <dataValidations>
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E7">
+      <formula1>1.0</formula1>
+      <formula2>7.0</formula2>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C13:C22 C31:C33 C43:C45 C54:C56 C65:C67">
+      <formula1>'RELEVANCIA-PUNTAJE'!$B$2:$E$2</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>'RELEVANCIA-PUNTAJE'!$B$2:$E$2</xm:f>
-          </x14:formula1>
-          <xm:sqref>C13:C22 C54:C56 C43:C45 C31:C33</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC27BBF0-2056-4C6C-A496-F3E7DD799403}">
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.42578125" customWidth="1"/>
-    <col min="2" max="2" width="40.28515625" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" customWidth="1"/>
-    <col min="4" max="4" width="38.7109375" customWidth="1"/>
-    <col min="5" max="5" width="38.42578125" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="39.43"/>
+    <col customWidth="1" min="2" max="2" width="40.29"/>
+    <col customWidth="1" min="3" max="3" width="31.71"/>
+    <col customWidth="1" min="4" max="4" width="38.71"/>
+    <col customWidth="1" min="5" max="5" width="38.43"/>
+    <col customWidth="1" min="6" max="26" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1"/>
-    <row r="2" spans="1:6" ht="15" thickBot="1">
-      <c r="A2" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="56"/>
-      <c r="B3" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="56"/>
-    </row>
-    <row r="4" spans="1:6" ht="57.6" customHeight="1" thickBot="1">
-      <c r="A4" s="57"/>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="26">
+    <row r="1" ht="14.25" customHeight="1"/>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="A2" s="43" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="43" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="47"/>
+    </row>
+    <row r="4" ht="57.0" customHeight="1">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="52">
         <v>-0.3</v>
       </c>
-      <c r="E4" s="26">
-        <v>0</v>
-      </c>
-      <c r="F4" s="57"/>
-    </row>
-    <row r="5" spans="1:6" ht="83.45" thickBot="1">
-      <c r="A5" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="83.45" thickBot="1">
-      <c r="A6" s="74" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="30">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="94.9" customHeight="1" thickBot="1">
-      <c r="A7" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="42" t="s">
+      <c r="E4" s="52">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="51"/>
+    </row>
+    <row r="5" ht="14.25" customHeight="1">
+      <c r="A5" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="B5" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="C5" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="D5" s="54" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="31">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="82.9">
-      <c r="A8" s="42" t="s">
+      <c r="E5" s="54" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="F5" s="55">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="56" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="B6" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="C6" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="D6" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="65.45" customHeight="1" thickBot="1">
-      <c r="A9" s="38" t="s">
+      <c r="E6" s="57" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="F6" s="58">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="7" ht="94.5" customHeight="1">
+      <c r="A7" s="59" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="B7" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="C7" s="59" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="D7" s="59" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="69.599999999999994" thickBot="1">
-      <c r="A10" s="38" t="s">
+      <c r="E7" s="59" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="F7" s="60">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25" customHeight="1">
+      <c r="A8" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="B8" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="C8" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="D8" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="69">
-      <c r="A11" s="74" t="s">
+      <c r="E8" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="74" t="s">
+      <c r="F8" s="60">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="9" ht="65.25" customHeight="1">
+      <c r="A9" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="B9" s="54" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="C9" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="E11" s="74" t="s">
+      <c r="D9" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="F11" s="30">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="55.15">
-      <c r="A12" s="76" t="s">
+      <c r="E9" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="75" t="s">
+      <c r="F9" s="55">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="10" ht="14.25" customHeight="1">
+      <c r="A10" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="C12" s="75" t="s">
+      <c r="B10" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="75" t="s">
+      <c r="C10" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="75" t="s">
+      <c r="D10" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="F12" s="40">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="94.15" customHeight="1">
-      <c r="A13" s="42" t="s">
+      <c r="E10" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="F10" s="55">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" customHeight="1">
+      <c r="A11" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="B11" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="C11" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="D11" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="F13" s="41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="69">
-      <c r="A14" s="42" t="s">
+      <c r="E11" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="F11" s="58">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1">
+      <c r="A12" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="B12" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="42" t="s">
+      <c r="C12" s="57" t="s">
         <v>72</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="D12" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="69.599999999999994" thickBot="1">
-      <c r="A15" s="38" t="s">
+      <c r="E12" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="F12" s="62">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="13" ht="93.75" customHeight="1">
+      <c r="A13" s="59" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="B13" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="C13" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="D13" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="F15" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="83.45" thickBot="1">
-      <c r="A16" s="38" t="s">
+      <c r="E13" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="F13" s="63">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="14" ht="14.25" customHeight="1">
+      <c r="A14" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="B14" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="C14" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="D14" s="59" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="97.15" thickBot="1">
-      <c r="A17" s="38" t="s">
+      <c r="E14" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="F14" s="63">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="B15" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="39" t="s">
+      <c r="C15" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="D15" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="F17" s="28">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1">
-      <c r="A18" s="52" t="s">
+      <c r="E15" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="29">
-        <v>1</v>
-      </c>
-    </row>
+      <c r="F15" s="55">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="55">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" customHeight="1">
+      <c r="A17" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="54" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" s="54" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="55">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="18" ht="14.25" customHeight="1">
+      <c r="A18" s="64" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="65">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="14.25" customHeight="1"/>
+    <row r="223" ht="14.25" customHeight="1"/>
+    <row r="224" ht="14.25" customHeight="1"/>
+    <row r="225" ht="14.25" customHeight="1"/>
+    <row r="226" ht="14.25" customHeight="1"/>
+    <row r="227" ht="14.25" customHeight="1"/>
+    <row r="228" ht="14.25" customHeight="1"/>
+    <row r="229" ht="14.25" customHeight="1"/>
+    <row r="230" ht="14.25" customHeight="1"/>
+    <row r="231" ht="14.25" customHeight="1"/>
+    <row r="232" ht="14.25" customHeight="1"/>
+    <row r="233" ht="14.25" customHeight="1"/>
+    <row r="234" ht="14.25" customHeight="1"/>
+    <row r="235" ht="14.25" customHeight="1"/>
+    <row r="236" ht="14.25" customHeight="1"/>
+    <row r="237" ht="14.25" customHeight="1"/>
+    <row r="238" ht="14.25" customHeight="1"/>
+    <row r="239" ht="14.25" customHeight="1"/>
+    <row r="240" ht="14.25" customHeight="1"/>
+    <row r="241" ht="14.25" customHeight="1"/>
+    <row r="242" ht="14.25" customHeight="1"/>
+    <row r="243" ht="14.25" customHeight="1"/>
+    <row r="244" ht="14.25" customHeight="1"/>
+    <row r="245" ht="14.25" customHeight="1"/>
+    <row r="246" ht="14.25" customHeight="1"/>
+    <row r="247" ht="14.25" customHeight="1"/>
+    <row r="248" ht="14.25" customHeight="1"/>
+    <row r="249" ht="14.25" customHeight="1"/>
+    <row r="250" ht="14.25" customHeight="1"/>
+    <row r="251" ht="14.25" customHeight="1"/>
+    <row r="252" ht="14.25" customHeight="1"/>
+    <row r="253" ht="14.25" customHeight="1"/>
+    <row r="254" ht="14.25" customHeight="1"/>
+    <row r="255" ht="14.25" customHeight="1"/>
+    <row r="256" ht="14.25" customHeight="1"/>
+    <row r="257" ht="14.25" customHeight="1"/>
+    <row r="258" ht="14.25" customHeight="1"/>
+    <row r="259" ht="14.25" customHeight="1"/>
+    <row r="260" ht="14.25" customHeight="1"/>
+    <row r="261" ht="14.25" customHeight="1"/>
+    <row r="262" ht="14.25" customHeight="1"/>
+    <row r="263" ht="14.25" customHeight="1"/>
+    <row r="264" ht="14.25" customHeight="1"/>
+    <row r="265" ht="14.25" customHeight="1"/>
+    <row r="266" ht="14.25" customHeight="1"/>
+    <row r="267" ht="14.25" customHeight="1"/>
+    <row r="268" ht="14.25" customHeight="1"/>
+    <row r="269" ht="14.25" customHeight="1"/>
+    <row r="270" ht="14.25" customHeight="1"/>
+    <row r="271" ht="14.25" customHeight="1"/>
+    <row r="272" ht="14.25" customHeight="1"/>
+    <row r="273" ht="14.25" customHeight="1"/>
+    <row r="274" ht="14.25" customHeight="1"/>
+    <row r="275" ht="14.25" customHeight="1"/>
+    <row r="276" ht="14.25" customHeight="1"/>
+    <row r="277" ht="14.25" customHeight="1"/>
+    <row r="278" ht="14.25" customHeight="1"/>
+    <row r="279" ht="14.25" customHeight="1"/>
+    <row r="280" ht="14.25" customHeight="1"/>
+    <row r="281" ht="14.25" customHeight="1"/>
+    <row r="282" ht="14.25" customHeight="1"/>
+    <row r="283" ht="14.25" customHeight="1"/>
+    <row r="284" ht="14.25" customHeight="1"/>
+    <row r="285" ht="14.25" customHeight="1"/>
+    <row r="286" ht="14.25" customHeight="1"/>
+    <row r="287" ht="14.25" customHeight="1"/>
+    <row r="288" ht="14.25" customHeight="1"/>
+    <row r="289" ht="14.25" customHeight="1"/>
+    <row r="290" ht="14.25" customHeight="1"/>
+    <row r="291" ht="14.25" customHeight="1"/>
+    <row r="292" ht="14.25" customHeight="1"/>
+    <row r="293" ht="14.25" customHeight="1"/>
+    <row r="294" ht="14.25" customHeight="1"/>
+    <row r="295" ht="14.25" customHeight="1"/>
+    <row r="296" ht="14.25" customHeight="1"/>
+    <row r="297" ht="14.25" customHeight="1"/>
+    <row r="298" ht="14.25" customHeight="1"/>
+    <row r="299" ht="14.25" customHeight="1"/>
+    <row r="300" ht="14.25" customHeight="1"/>
+    <row r="301" ht="14.25" customHeight="1"/>
+    <row r="302" ht="14.25" customHeight="1"/>
+    <row r="303" ht="14.25" customHeight="1"/>
+    <row r="304" ht="14.25" customHeight="1"/>
+    <row r="305" ht="14.25" customHeight="1"/>
+    <row r="306" ht="14.25" customHeight="1"/>
+    <row r="307" ht="14.25" customHeight="1"/>
+    <row r="308" ht="14.25" customHeight="1"/>
+    <row r="309" ht="14.25" customHeight="1"/>
+    <row r="310" ht="14.25" customHeight="1"/>
+    <row r="311" ht="14.25" customHeight="1"/>
+    <row r="312" ht="14.25" customHeight="1"/>
+    <row r="313" ht="14.25" customHeight="1"/>
+    <row r="314" ht="14.25" customHeight="1"/>
+    <row r="315" ht="14.25" customHeight="1"/>
+    <row r="316" ht="14.25" customHeight="1"/>
+    <row r="317" ht="14.25" customHeight="1"/>
+    <row r="318" ht="14.25" customHeight="1"/>
+    <row r="319" ht="14.25" customHeight="1"/>
+    <row r="320" ht="14.25" customHeight="1"/>
+    <row r="321" ht="14.25" customHeight="1"/>
+    <row r="322" ht="14.25" customHeight="1"/>
+    <row r="323" ht="14.25" customHeight="1"/>
+    <row r="324" ht="14.25" customHeight="1"/>
+    <row r="325" ht="14.25" customHeight="1"/>
+    <row r="326" ht="14.25" customHeight="1"/>
+    <row r="327" ht="14.25" customHeight="1"/>
+    <row r="328" ht="14.25" customHeight="1"/>
+    <row r="329" ht="14.25" customHeight="1"/>
+    <row r="330" ht="14.25" customHeight="1"/>
+    <row r="331" ht="14.25" customHeight="1"/>
+    <row r="332" ht="14.25" customHeight="1"/>
+    <row r="333" ht="14.25" customHeight="1"/>
+    <row r="334" ht="14.25" customHeight="1"/>
+    <row r="335" ht="14.25" customHeight="1"/>
+    <row r="336" ht="14.25" customHeight="1"/>
+    <row r="337" ht="14.25" customHeight="1"/>
+    <row r="338" ht="14.25" customHeight="1"/>
+    <row r="339" ht="14.25" customHeight="1"/>
+    <row r="340" ht="14.25" customHeight="1"/>
+    <row r="341" ht="14.25" customHeight="1"/>
+    <row r="342" ht="14.25" customHeight="1"/>
+    <row r="343" ht="14.25" customHeight="1"/>
+    <row r="344" ht="14.25" customHeight="1"/>
+    <row r="345" ht="14.25" customHeight="1"/>
+    <row r="346" ht="14.25" customHeight="1"/>
+    <row r="347" ht="14.25" customHeight="1"/>
+    <row r="348" ht="14.25" customHeight="1"/>
+    <row r="349" ht="14.25" customHeight="1"/>
+    <row r="350" ht="14.25" customHeight="1"/>
+    <row r="351" ht="14.25" customHeight="1"/>
+    <row r="352" ht="14.25" customHeight="1"/>
+    <row r="353" ht="14.25" customHeight="1"/>
+    <row r="354" ht="14.25" customHeight="1"/>
+    <row r="355" ht="14.25" customHeight="1"/>
+    <row r="356" ht="14.25" customHeight="1"/>
+    <row r="357" ht="14.25" customHeight="1"/>
+    <row r="358" ht="14.25" customHeight="1"/>
+    <row r="359" ht="14.25" customHeight="1"/>
+    <row r="360" ht="14.25" customHeight="1"/>
+    <row r="361" ht="14.25" customHeight="1"/>
+    <row r="362" ht="14.25" customHeight="1"/>
+    <row r="363" ht="14.25" customHeight="1"/>
+    <row r="364" ht="14.25" customHeight="1"/>
+    <row r="365" ht="14.25" customHeight="1"/>
+    <row r="366" ht="14.25" customHeight="1"/>
+    <row r="367" ht="14.25" customHeight="1"/>
+    <row r="368" ht="14.25" customHeight="1"/>
+    <row r="369" ht="14.25" customHeight="1"/>
+    <row r="370" ht="14.25" customHeight="1"/>
+    <row r="371" ht="14.25" customHeight="1"/>
+    <row r="372" ht="14.25" customHeight="1"/>
+    <row r="373" ht="14.25" customHeight="1"/>
+    <row r="374" ht="14.25" customHeight="1"/>
+    <row r="375" ht="14.25" customHeight="1"/>
+    <row r="376" ht="14.25" customHeight="1"/>
+    <row r="377" ht="14.25" customHeight="1"/>
+    <row r="378" ht="14.25" customHeight="1"/>
+    <row r="379" ht="14.25" customHeight="1"/>
+    <row r="380" ht="14.25" customHeight="1"/>
+    <row r="381" ht="14.25" customHeight="1"/>
+    <row r="382" ht="14.25" customHeight="1"/>
+    <row r="383" ht="14.25" customHeight="1"/>
+    <row r="384" ht="14.25" customHeight="1"/>
+    <row r="385" ht="14.25" customHeight="1"/>
+    <row r="386" ht="14.25" customHeight="1"/>
+    <row r="387" ht="14.25" customHeight="1"/>
+    <row r="388" ht="14.25" customHeight="1"/>
+    <row r="389" ht="14.25" customHeight="1"/>
+    <row r="390" ht="14.25" customHeight="1"/>
+    <row r="391" ht="14.25" customHeight="1"/>
+    <row r="392" ht="14.25" customHeight="1"/>
+    <row r="393" ht="14.25" customHeight="1"/>
+    <row r="394" ht="14.25" customHeight="1"/>
+    <row r="395" ht="14.25" customHeight="1"/>
+    <row r="396" ht="14.25" customHeight="1"/>
+    <row r="397" ht="14.25" customHeight="1"/>
+    <row r="398" ht="14.25" customHeight="1"/>
+    <row r="399" ht="14.25" customHeight="1"/>
+    <row r="400" ht="14.25" customHeight="1"/>
+    <row r="401" ht="14.25" customHeight="1"/>
+    <row r="402" ht="14.25" customHeight="1"/>
+    <row r="403" ht="14.25" customHeight="1"/>
+    <row r="404" ht="14.25" customHeight="1"/>
+    <row r="405" ht="14.25" customHeight="1"/>
+    <row r="406" ht="14.25" customHeight="1"/>
+    <row r="407" ht="14.25" customHeight="1"/>
+    <row r="408" ht="14.25" customHeight="1"/>
+    <row r="409" ht="14.25" customHeight="1"/>
+    <row r="410" ht="14.25" customHeight="1"/>
+    <row r="411" ht="14.25" customHeight="1"/>
+    <row r="412" ht="14.25" customHeight="1"/>
+    <row r="413" ht="14.25" customHeight="1"/>
+    <row r="414" ht="14.25" customHeight="1"/>
+    <row r="415" ht="14.25" customHeight="1"/>
+    <row r="416" ht="14.25" customHeight="1"/>
+    <row r="417" ht="14.25" customHeight="1"/>
+    <row r="418" ht="14.25" customHeight="1"/>
+    <row r="419" ht="14.25" customHeight="1"/>
+    <row r="420" ht="14.25" customHeight="1"/>
+    <row r="421" ht="14.25" customHeight="1"/>
+    <row r="422" ht="14.25" customHeight="1"/>
+    <row r="423" ht="14.25" customHeight="1"/>
+    <row r="424" ht="14.25" customHeight="1"/>
+    <row r="425" ht="14.25" customHeight="1"/>
+    <row r="426" ht="14.25" customHeight="1"/>
+    <row r="427" ht="14.25" customHeight="1"/>
+    <row r="428" ht="14.25" customHeight="1"/>
+    <row r="429" ht="14.25" customHeight="1"/>
+    <row r="430" ht="14.25" customHeight="1"/>
+    <row r="431" ht="14.25" customHeight="1"/>
+    <row r="432" ht="14.25" customHeight="1"/>
+    <row r="433" ht="14.25" customHeight="1"/>
+    <row r="434" ht="14.25" customHeight="1"/>
+    <row r="435" ht="14.25" customHeight="1"/>
+    <row r="436" ht="14.25" customHeight="1"/>
+    <row r="437" ht="14.25" customHeight="1"/>
+    <row r="438" ht="14.25" customHeight="1"/>
+    <row r="439" ht="14.25" customHeight="1"/>
+    <row r="440" ht="14.25" customHeight="1"/>
+    <row r="441" ht="14.25" customHeight="1"/>
+    <row r="442" ht="14.25" customHeight="1"/>
+    <row r="443" ht="14.25" customHeight="1"/>
+    <row r="444" ht="14.25" customHeight="1"/>
+    <row r="445" ht="14.25" customHeight="1"/>
+    <row r="446" ht="14.25" customHeight="1"/>
+    <row r="447" ht="14.25" customHeight="1"/>
+    <row r="448" ht="14.25" customHeight="1"/>
+    <row r="449" ht="14.25" customHeight="1"/>
+    <row r="450" ht="14.25" customHeight="1"/>
+    <row r="451" ht="14.25" customHeight="1"/>
+    <row r="452" ht="14.25" customHeight="1"/>
+    <row r="453" ht="14.25" customHeight="1"/>
+    <row r="454" ht="14.25" customHeight="1"/>
+    <row r="455" ht="14.25" customHeight="1"/>
+    <row r="456" ht="14.25" customHeight="1"/>
+    <row r="457" ht="14.25" customHeight="1"/>
+    <row r="458" ht="14.25" customHeight="1"/>
+    <row r="459" ht="14.25" customHeight="1"/>
+    <row r="460" ht="14.25" customHeight="1"/>
+    <row r="461" ht="14.25" customHeight="1"/>
+    <row r="462" ht="14.25" customHeight="1"/>
+    <row r="463" ht="14.25" customHeight="1"/>
+    <row r="464" ht="14.25" customHeight="1"/>
+    <row r="465" ht="14.25" customHeight="1"/>
+    <row r="466" ht="14.25" customHeight="1"/>
+    <row r="467" ht="14.25" customHeight="1"/>
+    <row r="468" ht="14.25" customHeight="1"/>
+    <row r="469" ht="14.25" customHeight="1"/>
+    <row r="470" ht="14.25" customHeight="1"/>
+    <row r="471" ht="14.25" customHeight="1"/>
+    <row r="472" ht="14.25" customHeight="1"/>
+    <row r="473" ht="14.25" customHeight="1"/>
+    <row r="474" ht="14.25" customHeight="1"/>
+    <row r="475" ht="14.25" customHeight="1"/>
+    <row r="476" ht="14.25" customHeight="1"/>
+    <row r="477" ht="14.25" customHeight="1"/>
+    <row r="478" ht="14.25" customHeight="1"/>
+    <row r="479" ht="14.25" customHeight="1"/>
+    <row r="480" ht="14.25" customHeight="1"/>
+    <row r="481" ht="14.25" customHeight="1"/>
+    <row r="482" ht="14.25" customHeight="1"/>
+    <row r="483" ht="14.25" customHeight="1"/>
+    <row r="484" ht="14.25" customHeight="1"/>
+    <row r="485" ht="14.25" customHeight="1"/>
+    <row r="486" ht="14.25" customHeight="1"/>
+    <row r="487" ht="14.25" customHeight="1"/>
+    <row r="488" ht="14.25" customHeight="1"/>
+    <row r="489" ht="14.25" customHeight="1"/>
+    <row r="490" ht="14.25" customHeight="1"/>
+    <row r="491" ht="14.25" customHeight="1"/>
+    <row r="492" ht="14.25" customHeight="1"/>
+    <row r="493" ht="14.25" customHeight="1"/>
+    <row r="494" ht="14.25" customHeight="1"/>
+    <row r="495" ht="14.25" customHeight="1"/>
+    <row r="496" ht="14.25" customHeight="1"/>
+    <row r="497" ht="14.25" customHeight="1"/>
+    <row r="498" ht="14.25" customHeight="1"/>
+    <row r="499" ht="14.25" customHeight="1"/>
+    <row r="500" ht="14.25" customHeight="1"/>
+    <row r="501" ht="14.25" customHeight="1"/>
+    <row r="502" ht="14.25" customHeight="1"/>
+    <row r="503" ht="14.25" customHeight="1"/>
+    <row r="504" ht="14.25" customHeight="1"/>
+    <row r="505" ht="14.25" customHeight="1"/>
+    <row r="506" ht="14.25" customHeight="1"/>
+    <row r="507" ht="14.25" customHeight="1"/>
+    <row r="508" ht="14.25" customHeight="1"/>
+    <row r="509" ht="14.25" customHeight="1"/>
+    <row r="510" ht="14.25" customHeight="1"/>
+    <row r="511" ht="14.25" customHeight="1"/>
+    <row r="512" ht="14.25" customHeight="1"/>
+    <row r="513" ht="14.25" customHeight="1"/>
+    <row r="514" ht="14.25" customHeight="1"/>
+    <row r="515" ht="14.25" customHeight="1"/>
+    <row r="516" ht="14.25" customHeight="1"/>
+    <row r="517" ht="14.25" customHeight="1"/>
+    <row r="518" ht="14.25" customHeight="1"/>
+    <row r="519" ht="14.25" customHeight="1"/>
+    <row r="520" ht="14.25" customHeight="1"/>
+    <row r="521" ht="14.25" customHeight="1"/>
+    <row r="522" ht="14.25" customHeight="1"/>
+    <row r="523" ht="14.25" customHeight="1"/>
+    <row r="524" ht="14.25" customHeight="1"/>
+    <row r="525" ht="14.25" customHeight="1"/>
+    <row r="526" ht="14.25" customHeight="1"/>
+    <row r="527" ht="14.25" customHeight="1"/>
+    <row r="528" ht="14.25" customHeight="1"/>
+    <row r="529" ht="14.25" customHeight="1"/>
+    <row r="530" ht="14.25" customHeight="1"/>
+    <row r="531" ht="14.25" customHeight="1"/>
+    <row r="532" ht="14.25" customHeight="1"/>
+    <row r="533" ht="14.25" customHeight="1"/>
+    <row r="534" ht="14.25" customHeight="1"/>
+    <row r="535" ht="14.25" customHeight="1"/>
+    <row r="536" ht="14.25" customHeight="1"/>
+    <row r="537" ht="14.25" customHeight="1"/>
+    <row r="538" ht="14.25" customHeight="1"/>
+    <row r="539" ht="14.25" customHeight="1"/>
+    <row r="540" ht="14.25" customHeight="1"/>
+    <row r="541" ht="14.25" customHeight="1"/>
+    <row r="542" ht="14.25" customHeight="1"/>
+    <row r="543" ht="14.25" customHeight="1"/>
+    <row r="544" ht="14.25" customHeight="1"/>
+    <row r="545" ht="14.25" customHeight="1"/>
+    <row r="546" ht="14.25" customHeight="1"/>
+    <row r="547" ht="14.25" customHeight="1"/>
+    <row r="548" ht="14.25" customHeight="1"/>
+    <row r="549" ht="14.25" customHeight="1"/>
+    <row r="550" ht="14.25" customHeight="1"/>
+    <row r="551" ht="14.25" customHeight="1"/>
+    <row r="552" ht="14.25" customHeight="1"/>
+    <row r="553" ht="14.25" customHeight="1"/>
+    <row r="554" ht="14.25" customHeight="1"/>
+    <row r="555" ht="14.25" customHeight="1"/>
+    <row r="556" ht="14.25" customHeight="1"/>
+    <row r="557" ht="14.25" customHeight="1"/>
+    <row r="558" ht="14.25" customHeight="1"/>
+    <row r="559" ht="14.25" customHeight="1"/>
+    <row r="560" ht="14.25" customHeight="1"/>
+    <row r="561" ht="14.25" customHeight="1"/>
+    <row r="562" ht="14.25" customHeight="1"/>
+    <row r="563" ht="14.25" customHeight="1"/>
+    <row r="564" ht="14.25" customHeight="1"/>
+    <row r="565" ht="14.25" customHeight="1"/>
+    <row r="566" ht="14.25" customHeight="1"/>
+    <row r="567" ht="14.25" customHeight="1"/>
+    <row r="568" ht="14.25" customHeight="1"/>
+    <row r="569" ht="14.25" customHeight="1"/>
+    <row r="570" ht="14.25" customHeight="1"/>
+    <row r="571" ht="14.25" customHeight="1"/>
+    <row r="572" ht="14.25" customHeight="1"/>
+    <row r="573" ht="14.25" customHeight="1"/>
+    <row r="574" ht="14.25" customHeight="1"/>
+    <row r="575" ht="14.25" customHeight="1"/>
+    <row r="576" ht="14.25" customHeight="1"/>
+    <row r="577" ht="14.25" customHeight="1"/>
+    <row r="578" ht="14.25" customHeight="1"/>
+    <row r="579" ht="14.25" customHeight="1"/>
+    <row r="580" ht="14.25" customHeight="1"/>
+    <row r="581" ht="14.25" customHeight="1"/>
+    <row r="582" ht="14.25" customHeight="1"/>
+    <row r="583" ht="14.25" customHeight="1"/>
+    <row r="584" ht="14.25" customHeight="1"/>
+    <row r="585" ht="14.25" customHeight="1"/>
+    <row r="586" ht="14.25" customHeight="1"/>
+    <row r="587" ht="14.25" customHeight="1"/>
+    <row r="588" ht="14.25" customHeight="1"/>
+    <row r="589" ht="14.25" customHeight="1"/>
+    <row r="590" ht="14.25" customHeight="1"/>
+    <row r="591" ht="14.25" customHeight="1"/>
+    <row r="592" ht="14.25" customHeight="1"/>
+    <row r="593" ht="14.25" customHeight="1"/>
+    <row r="594" ht="14.25" customHeight="1"/>
+    <row r="595" ht="14.25" customHeight="1"/>
+    <row r="596" ht="14.25" customHeight="1"/>
+    <row r="597" ht="14.25" customHeight="1"/>
+    <row r="598" ht="14.25" customHeight="1"/>
+    <row r="599" ht="14.25" customHeight="1"/>
+    <row r="600" ht="14.25" customHeight="1"/>
+    <row r="601" ht="14.25" customHeight="1"/>
+    <row r="602" ht="14.25" customHeight="1"/>
+    <row r="603" ht="14.25" customHeight="1"/>
+    <row r="604" ht="14.25" customHeight="1"/>
+    <row r="605" ht="14.25" customHeight="1"/>
+    <row r="606" ht="14.25" customHeight="1"/>
+    <row r="607" ht="14.25" customHeight="1"/>
+    <row r="608" ht="14.25" customHeight="1"/>
+    <row r="609" ht="14.25" customHeight="1"/>
+    <row r="610" ht="14.25" customHeight="1"/>
+    <row r="611" ht="14.25" customHeight="1"/>
+    <row r="612" ht="14.25" customHeight="1"/>
+    <row r="613" ht="14.25" customHeight="1"/>
+    <row r="614" ht="14.25" customHeight="1"/>
+    <row r="615" ht="14.25" customHeight="1"/>
+    <row r="616" ht="14.25" customHeight="1"/>
+    <row r="617" ht="14.25" customHeight="1"/>
+    <row r="618" ht="14.25" customHeight="1"/>
+    <row r="619" ht="14.25" customHeight="1"/>
+    <row r="620" ht="14.25" customHeight="1"/>
+    <row r="621" ht="14.25" customHeight="1"/>
+    <row r="622" ht="14.25" customHeight="1"/>
+    <row r="623" ht="14.25" customHeight="1"/>
+    <row r="624" ht="14.25" customHeight="1"/>
+    <row r="625" ht="14.25" customHeight="1"/>
+    <row r="626" ht="14.25" customHeight="1"/>
+    <row r="627" ht="14.25" customHeight="1"/>
+    <row r="628" ht="14.25" customHeight="1"/>
+    <row r="629" ht="14.25" customHeight="1"/>
+    <row r="630" ht="14.25" customHeight="1"/>
+    <row r="631" ht="14.25" customHeight="1"/>
+    <row r="632" ht="14.25" customHeight="1"/>
+    <row r="633" ht="14.25" customHeight="1"/>
+    <row r="634" ht="14.25" customHeight="1"/>
+    <row r="635" ht="14.25" customHeight="1"/>
+    <row r="636" ht="14.25" customHeight="1"/>
+    <row r="637" ht="14.25" customHeight="1"/>
+    <row r="638" ht="14.25" customHeight="1"/>
+    <row r="639" ht="14.25" customHeight="1"/>
+    <row r="640" ht="14.25" customHeight="1"/>
+    <row r="641" ht="14.25" customHeight="1"/>
+    <row r="642" ht="14.25" customHeight="1"/>
+    <row r="643" ht="14.25" customHeight="1"/>
+    <row r="644" ht="14.25" customHeight="1"/>
+    <row r="645" ht="14.25" customHeight="1"/>
+    <row r="646" ht="14.25" customHeight="1"/>
+    <row r="647" ht="14.25" customHeight="1"/>
+    <row r="648" ht="14.25" customHeight="1"/>
+    <row r="649" ht="14.25" customHeight="1"/>
+    <row r="650" ht="14.25" customHeight="1"/>
+    <row r="651" ht="14.25" customHeight="1"/>
+    <row r="652" ht="14.25" customHeight="1"/>
+    <row r="653" ht="14.25" customHeight="1"/>
+    <row r="654" ht="14.25" customHeight="1"/>
+    <row r="655" ht="14.25" customHeight="1"/>
+    <row r="656" ht="14.25" customHeight="1"/>
+    <row r="657" ht="14.25" customHeight="1"/>
+    <row r="658" ht="14.25" customHeight="1"/>
+    <row r="659" ht="14.25" customHeight="1"/>
+    <row r="660" ht="14.25" customHeight="1"/>
+    <row r="661" ht="14.25" customHeight="1"/>
+    <row r="662" ht="14.25" customHeight="1"/>
+    <row r="663" ht="14.25" customHeight="1"/>
+    <row r="664" ht="14.25" customHeight="1"/>
+    <row r="665" ht="14.25" customHeight="1"/>
+    <row r="666" ht="14.25" customHeight="1"/>
+    <row r="667" ht="14.25" customHeight="1"/>
+    <row r="668" ht="14.25" customHeight="1"/>
+    <row r="669" ht="14.25" customHeight="1"/>
+    <row r="670" ht="14.25" customHeight="1"/>
+    <row r="671" ht="14.25" customHeight="1"/>
+    <row r="672" ht="14.25" customHeight="1"/>
+    <row r="673" ht="14.25" customHeight="1"/>
+    <row r="674" ht="14.25" customHeight="1"/>
+    <row r="675" ht="14.25" customHeight="1"/>
+    <row r="676" ht="14.25" customHeight="1"/>
+    <row r="677" ht="14.25" customHeight="1"/>
+    <row r="678" ht="14.25" customHeight="1"/>
+    <row r="679" ht="14.25" customHeight="1"/>
+    <row r="680" ht="14.25" customHeight="1"/>
+    <row r="681" ht="14.25" customHeight="1"/>
+    <row r="682" ht="14.25" customHeight="1"/>
+    <row r="683" ht="14.25" customHeight="1"/>
+    <row r="684" ht="14.25" customHeight="1"/>
+    <row r="685" ht="14.25" customHeight="1"/>
+    <row r="686" ht="14.25" customHeight="1"/>
+    <row r="687" ht="14.25" customHeight="1"/>
+    <row r="688" ht="14.25" customHeight="1"/>
+    <row r="689" ht="14.25" customHeight="1"/>
+    <row r="690" ht="14.25" customHeight="1"/>
+    <row r="691" ht="14.25" customHeight="1"/>
+    <row r="692" ht="14.25" customHeight="1"/>
+    <row r="693" ht="14.25" customHeight="1"/>
+    <row r="694" ht="14.25" customHeight="1"/>
+    <row r="695" ht="14.25" customHeight="1"/>
+    <row r="696" ht="14.25" customHeight="1"/>
+    <row r="697" ht="14.25" customHeight="1"/>
+    <row r="698" ht="14.25" customHeight="1"/>
+    <row r="699" ht="14.25" customHeight="1"/>
+    <row r="700" ht="14.25" customHeight="1"/>
+    <row r="701" ht="14.25" customHeight="1"/>
+    <row r="702" ht="14.25" customHeight="1"/>
+    <row r="703" ht="14.25" customHeight="1"/>
+    <row r="704" ht="14.25" customHeight="1"/>
+    <row r="705" ht="14.25" customHeight="1"/>
+    <row r="706" ht="14.25" customHeight="1"/>
+    <row r="707" ht="14.25" customHeight="1"/>
+    <row r="708" ht="14.25" customHeight="1"/>
+    <row r="709" ht="14.25" customHeight="1"/>
+    <row r="710" ht="14.25" customHeight="1"/>
+    <row r="711" ht="14.25" customHeight="1"/>
+    <row r="712" ht="14.25" customHeight="1"/>
+    <row r="713" ht="14.25" customHeight="1"/>
+    <row r="714" ht="14.25" customHeight="1"/>
+    <row r="715" ht="14.25" customHeight="1"/>
+    <row r="716" ht="14.25" customHeight="1"/>
+    <row r="717" ht="14.25" customHeight="1"/>
+    <row r="718" ht="14.25" customHeight="1"/>
+    <row r="719" ht="14.25" customHeight="1"/>
+    <row r="720" ht="14.25" customHeight="1"/>
+    <row r="721" ht="14.25" customHeight="1"/>
+    <row r="722" ht="14.25" customHeight="1"/>
+    <row r="723" ht="14.25" customHeight="1"/>
+    <row r="724" ht="14.25" customHeight="1"/>
+    <row r="725" ht="14.25" customHeight="1"/>
+    <row r="726" ht="14.25" customHeight="1"/>
+    <row r="727" ht="14.25" customHeight="1"/>
+    <row r="728" ht="14.25" customHeight="1"/>
+    <row r="729" ht="14.25" customHeight="1"/>
+    <row r="730" ht="14.25" customHeight="1"/>
+    <row r="731" ht="14.25" customHeight="1"/>
+    <row r="732" ht="14.25" customHeight="1"/>
+    <row r="733" ht="14.25" customHeight="1"/>
+    <row r="734" ht="14.25" customHeight="1"/>
+    <row r="735" ht="14.25" customHeight="1"/>
+    <row r="736" ht="14.25" customHeight="1"/>
+    <row r="737" ht="14.25" customHeight="1"/>
+    <row r="738" ht="14.25" customHeight="1"/>
+    <row r="739" ht="14.25" customHeight="1"/>
+    <row r="740" ht="14.25" customHeight="1"/>
+    <row r="741" ht="14.25" customHeight="1"/>
+    <row r="742" ht="14.25" customHeight="1"/>
+    <row r="743" ht="14.25" customHeight="1"/>
+    <row r="744" ht="14.25" customHeight="1"/>
+    <row r="745" ht="14.25" customHeight="1"/>
+    <row r="746" ht="14.25" customHeight="1"/>
+    <row r="747" ht="14.25" customHeight="1"/>
+    <row r="748" ht="14.25" customHeight="1"/>
+    <row r="749" ht="14.25" customHeight="1"/>
+    <row r="750" ht="14.25" customHeight="1"/>
+    <row r="751" ht="14.25" customHeight="1"/>
+    <row r="752" ht="14.25" customHeight="1"/>
+    <row r="753" ht="14.25" customHeight="1"/>
+    <row r="754" ht="14.25" customHeight="1"/>
+    <row r="755" ht="14.25" customHeight="1"/>
+    <row r="756" ht="14.25" customHeight="1"/>
+    <row r="757" ht="14.25" customHeight="1"/>
+    <row r="758" ht="14.25" customHeight="1"/>
+    <row r="759" ht="14.25" customHeight="1"/>
+    <row r="760" ht="14.25" customHeight="1"/>
+    <row r="761" ht="14.25" customHeight="1"/>
+    <row r="762" ht="14.25" customHeight="1"/>
+    <row r="763" ht="14.25" customHeight="1"/>
+    <row r="764" ht="14.25" customHeight="1"/>
+    <row r="765" ht="14.25" customHeight="1"/>
+    <row r="766" ht="14.25" customHeight="1"/>
+    <row r="767" ht="14.25" customHeight="1"/>
+    <row r="768" ht="14.25" customHeight="1"/>
+    <row r="769" ht="14.25" customHeight="1"/>
+    <row r="770" ht="14.25" customHeight="1"/>
+    <row r="771" ht="14.25" customHeight="1"/>
+    <row r="772" ht="14.25" customHeight="1"/>
+    <row r="773" ht="14.25" customHeight="1"/>
+    <row r="774" ht="14.25" customHeight="1"/>
+    <row r="775" ht="14.25" customHeight="1"/>
+    <row r="776" ht="14.25" customHeight="1"/>
+    <row r="777" ht="14.25" customHeight="1"/>
+    <row r="778" ht="14.25" customHeight="1"/>
+    <row r="779" ht="14.25" customHeight="1"/>
+    <row r="780" ht="14.25" customHeight="1"/>
+    <row r="781" ht="14.25" customHeight="1"/>
+    <row r="782" ht="14.25" customHeight="1"/>
+    <row r="783" ht="14.25" customHeight="1"/>
+    <row r="784" ht="14.25" customHeight="1"/>
+    <row r="785" ht="14.25" customHeight="1"/>
+    <row r="786" ht="14.25" customHeight="1"/>
+    <row r="787" ht="14.25" customHeight="1"/>
+    <row r="788" ht="14.25" customHeight="1"/>
+    <row r="789" ht="14.25" customHeight="1"/>
+    <row r="790" ht="14.25" customHeight="1"/>
+    <row r="791" ht="14.25" customHeight="1"/>
+    <row r="792" ht="14.25" customHeight="1"/>
+    <row r="793" ht="14.25" customHeight="1"/>
+    <row r="794" ht="14.25" customHeight="1"/>
+    <row r="795" ht="14.25" customHeight="1"/>
+    <row r="796" ht="14.25" customHeight="1"/>
+    <row r="797" ht="14.25" customHeight="1"/>
+    <row r="798" ht="14.25" customHeight="1"/>
+    <row r="799" ht="14.25" customHeight="1"/>
+    <row r="800" ht="14.25" customHeight="1"/>
+    <row r="801" ht="14.25" customHeight="1"/>
+    <row r="802" ht="14.25" customHeight="1"/>
+    <row r="803" ht="14.25" customHeight="1"/>
+    <row r="804" ht="14.25" customHeight="1"/>
+    <row r="805" ht="14.25" customHeight="1"/>
+    <row r="806" ht="14.25" customHeight="1"/>
+    <row r="807" ht="14.25" customHeight="1"/>
+    <row r="808" ht="14.25" customHeight="1"/>
+    <row r="809" ht="14.25" customHeight="1"/>
+    <row r="810" ht="14.25" customHeight="1"/>
+    <row r="811" ht="14.25" customHeight="1"/>
+    <row r="812" ht="14.25" customHeight="1"/>
+    <row r="813" ht="14.25" customHeight="1"/>
+    <row r="814" ht="14.25" customHeight="1"/>
+    <row r="815" ht="14.25" customHeight="1"/>
+    <row r="816" ht="14.25" customHeight="1"/>
+    <row r="817" ht="14.25" customHeight="1"/>
+    <row r="818" ht="14.25" customHeight="1"/>
+    <row r="819" ht="14.25" customHeight="1"/>
+    <row r="820" ht="14.25" customHeight="1"/>
+    <row r="821" ht="14.25" customHeight="1"/>
+    <row r="822" ht="14.25" customHeight="1"/>
+    <row r="823" ht="14.25" customHeight="1"/>
+    <row r="824" ht="14.25" customHeight="1"/>
+    <row r="825" ht="14.25" customHeight="1"/>
+    <row r="826" ht="14.25" customHeight="1"/>
+    <row r="827" ht="14.25" customHeight="1"/>
+    <row r="828" ht="14.25" customHeight="1"/>
+    <row r="829" ht="14.25" customHeight="1"/>
+    <row r="830" ht="14.25" customHeight="1"/>
+    <row r="831" ht="14.25" customHeight="1"/>
+    <row r="832" ht="14.25" customHeight="1"/>
+    <row r="833" ht="14.25" customHeight="1"/>
+    <row r="834" ht="14.25" customHeight="1"/>
+    <row r="835" ht="14.25" customHeight="1"/>
+    <row r="836" ht="14.25" customHeight="1"/>
+    <row r="837" ht="14.25" customHeight="1"/>
+    <row r="838" ht="14.25" customHeight="1"/>
+    <row r="839" ht="14.25" customHeight="1"/>
+    <row r="840" ht="14.25" customHeight="1"/>
+    <row r="841" ht="14.25" customHeight="1"/>
+    <row r="842" ht="14.25" customHeight="1"/>
+    <row r="843" ht="14.25" customHeight="1"/>
+    <row r="844" ht="14.25" customHeight="1"/>
+    <row r="845" ht="14.25" customHeight="1"/>
+    <row r="846" ht="14.25" customHeight="1"/>
+    <row r="847" ht="14.25" customHeight="1"/>
+    <row r="848" ht="14.25" customHeight="1"/>
+    <row r="849" ht="14.25" customHeight="1"/>
+    <row r="850" ht="14.25" customHeight="1"/>
+    <row r="851" ht="14.25" customHeight="1"/>
+    <row r="852" ht="14.25" customHeight="1"/>
+    <row r="853" ht="14.25" customHeight="1"/>
+    <row r="854" ht="14.25" customHeight="1"/>
+    <row r="855" ht="14.25" customHeight="1"/>
+    <row r="856" ht="14.25" customHeight="1"/>
+    <row r="857" ht="14.25" customHeight="1"/>
+    <row r="858" ht="14.25" customHeight="1"/>
+    <row r="859" ht="14.25" customHeight="1"/>
+    <row r="860" ht="14.25" customHeight="1"/>
+    <row r="861" ht="14.25" customHeight="1"/>
+    <row r="862" ht="14.25" customHeight="1"/>
+    <row r="863" ht="14.25" customHeight="1"/>
+    <row r="864" ht="14.25" customHeight="1"/>
+    <row r="865" ht="14.25" customHeight="1"/>
+    <row r="866" ht="14.25" customHeight="1"/>
+    <row r="867" ht="14.25" customHeight="1"/>
+    <row r="868" ht="14.25" customHeight="1"/>
+    <row r="869" ht="14.25" customHeight="1"/>
+    <row r="870" ht="14.25" customHeight="1"/>
+    <row r="871" ht="14.25" customHeight="1"/>
+    <row r="872" ht="14.25" customHeight="1"/>
+    <row r="873" ht="14.25" customHeight="1"/>
+    <row r="874" ht="14.25" customHeight="1"/>
+    <row r="875" ht="14.25" customHeight="1"/>
+    <row r="876" ht="14.25" customHeight="1"/>
+    <row r="877" ht="14.25" customHeight="1"/>
+    <row r="878" ht="14.25" customHeight="1"/>
+    <row r="879" ht="14.25" customHeight="1"/>
+    <row r="880" ht="14.25" customHeight="1"/>
+    <row r="881" ht="14.25" customHeight="1"/>
+    <row r="882" ht="14.25" customHeight="1"/>
+    <row r="883" ht="14.25" customHeight="1"/>
+    <row r="884" ht="14.25" customHeight="1"/>
+    <row r="885" ht="14.25" customHeight="1"/>
+    <row r="886" ht="14.25" customHeight="1"/>
+    <row r="887" ht="14.25" customHeight="1"/>
+    <row r="888" ht="14.25" customHeight="1"/>
+    <row r="889" ht="14.25" customHeight="1"/>
+    <row r="890" ht="14.25" customHeight="1"/>
+    <row r="891" ht="14.25" customHeight="1"/>
+    <row r="892" ht="14.25" customHeight="1"/>
+    <row r="893" ht="14.25" customHeight="1"/>
+    <row r="894" ht="14.25" customHeight="1"/>
+    <row r="895" ht="14.25" customHeight="1"/>
+    <row r="896" ht="14.25" customHeight="1"/>
+    <row r="897" ht="14.25" customHeight="1"/>
+    <row r="898" ht="14.25" customHeight="1"/>
+    <row r="899" ht="14.25" customHeight="1"/>
+    <row r="900" ht="14.25" customHeight="1"/>
+    <row r="901" ht="14.25" customHeight="1"/>
+    <row r="902" ht="14.25" customHeight="1"/>
+    <row r="903" ht="14.25" customHeight="1"/>
+    <row r="904" ht="14.25" customHeight="1"/>
+    <row r="905" ht="14.25" customHeight="1"/>
+    <row r="906" ht="14.25" customHeight="1"/>
+    <row r="907" ht="14.25" customHeight="1"/>
+    <row r="908" ht="14.25" customHeight="1"/>
+    <row r="909" ht="14.25" customHeight="1"/>
+    <row r="910" ht="14.25" customHeight="1"/>
+    <row r="911" ht="14.25" customHeight="1"/>
+    <row r="912" ht="14.25" customHeight="1"/>
+    <row r="913" ht="14.25" customHeight="1"/>
+    <row r="914" ht="14.25" customHeight="1"/>
+    <row r="915" ht="14.25" customHeight="1"/>
+    <row r="916" ht="14.25" customHeight="1"/>
+    <row r="917" ht="14.25" customHeight="1"/>
+    <row r="918" ht="14.25" customHeight="1"/>
+    <row r="919" ht="14.25" customHeight="1"/>
+    <row r="920" ht="14.25" customHeight="1"/>
+    <row r="921" ht="14.25" customHeight="1"/>
+    <row r="922" ht="14.25" customHeight="1"/>
+    <row r="923" ht="14.25" customHeight="1"/>
+    <row r="924" ht="14.25" customHeight="1"/>
+    <row r="925" ht="14.25" customHeight="1"/>
+    <row r="926" ht="14.25" customHeight="1"/>
+    <row r="927" ht="14.25" customHeight="1"/>
+    <row r="928" ht="14.25" customHeight="1"/>
+    <row r="929" ht="14.25" customHeight="1"/>
+    <row r="930" ht="14.25" customHeight="1"/>
+    <row r="931" ht="14.25" customHeight="1"/>
+    <row r="932" ht="14.25" customHeight="1"/>
+    <row r="933" ht="14.25" customHeight="1"/>
+    <row r="934" ht="14.25" customHeight="1"/>
+    <row r="935" ht="14.25" customHeight="1"/>
+    <row r="936" ht="14.25" customHeight="1"/>
+    <row r="937" ht="14.25" customHeight="1"/>
+    <row r="938" ht="14.25" customHeight="1"/>
+    <row r="939" ht="14.25" customHeight="1"/>
+    <row r="940" ht="14.25" customHeight="1"/>
+    <row r="941" ht="14.25" customHeight="1"/>
+    <row r="942" ht="14.25" customHeight="1"/>
+    <row r="943" ht="14.25" customHeight="1"/>
+    <row r="944" ht="14.25" customHeight="1"/>
+    <row r="945" ht="14.25" customHeight="1"/>
+    <row r="946" ht="14.25" customHeight="1"/>
+    <row r="947" ht="14.25" customHeight="1"/>
+    <row r="948" ht="14.25" customHeight="1"/>
+    <row r="949" ht="14.25" customHeight="1"/>
+    <row r="950" ht="14.25" customHeight="1"/>
+    <row r="951" ht="14.25" customHeight="1"/>
+    <row r="952" ht="14.25" customHeight="1"/>
+    <row r="953" ht="14.25" customHeight="1"/>
+    <row r="954" ht="14.25" customHeight="1"/>
+    <row r="955" ht="14.25" customHeight="1"/>
+    <row r="956" ht="14.25" customHeight="1"/>
+    <row r="957" ht="14.25" customHeight="1"/>
+    <row r="958" ht="14.25" customHeight="1"/>
+    <row r="959" ht="14.25" customHeight="1"/>
+    <row r="960" ht="14.25" customHeight="1"/>
+    <row r="961" ht="14.25" customHeight="1"/>
+    <row r="962" ht="14.25" customHeight="1"/>
+    <row r="963" ht="14.25" customHeight="1"/>
+    <row r="964" ht="14.25" customHeight="1"/>
+    <row r="965" ht="14.25" customHeight="1"/>
+    <row r="966" ht="14.25" customHeight="1"/>
+    <row r="967" ht="14.25" customHeight="1"/>
+    <row r="968" ht="14.25" customHeight="1"/>
+    <row r="969" ht="14.25" customHeight="1"/>
+    <row r="970" ht="14.25" customHeight="1"/>
+    <row r="971" ht="14.25" customHeight="1"/>
+    <row r="972" ht="14.25" customHeight="1"/>
+    <row r="973" ht="14.25" customHeight="1"/>
+    <row r="974" ht="14.25" customHeight="1"/>
+    <row r="975" ht="14.25" customHeight="1"/>
+    <row r="976" ht="14.25" customHeight="1"/>
+    <row r="977" ht="14.25" customHeight="1"/>
+    <row r="978" ht="14.25" customHeight="1"/>
+    <row r="979" ht="14.25" customHeight="1"/>
+    <row r="980" ht="14.25" customHeight="1"/>
+    <row r="981" ht="14.25" customHeight="1"/>
+    <row r="982" ht="14.25" customHeight="1"/>
+    <row r="983" ht="14.25" customHeight="1"/>
+    <row r="984" ht="14.25" customHeight="1"/>
+    <row r="985" ht="14.25" customHeight="1"/>
+    <row r="986" ht="14.25" customHeight="1"/>
+    <row r="987" ht="14.25" customHeight="1"/>
+    <row r="988" ht="14.25" customHeight="1"/>
+    <row r="989" ht="14.25" customHeight="1"/>
+    <row r="990" ht="14.25" customHeight="1"/>
+    <row r="991" ht="14.25" customHeight="1"/>
+    <row r="992" ht="14.25" customHeight="1"/>
+    <row r="993" ht="14.25" customHeight="1"/>
+    <row r="994" ht="14.25" customHeight="1"/>
+    <row r="995" ht="14.25" customHeight="1"/>
+    <row r="996" ht="14.25" customHeight="1"/>
+    <row r="997" ht="14.25" customHeight="1"/>
+    <row r="998" ht="14.25" customHeight="1"/>
+    <row r="999" ht="14.25" customHeight="1"/>
+    <row r="1000" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:F4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="21" width="10.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="14.45">
-      <c r="A3">
+    <row r="1">
+      <c r="A1" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="66">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="67">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="66">
         <v>0.5</v>
       </c>
-      <c r="B3" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="14.45">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="44">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="14.45">
-      <c r="A5">
+      <c r="B3" s="67">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="66">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="67">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66">
         <v>1.5</v>
       </c>
-      <c r="B5" s="44">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="14.45">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="44">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="14.45">
-      <c r="A7">
+      <c r="B5" s="67">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="66">
+        <v>2.0</v>
+      </c>
+      <c r="B6" s="67">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="66">
         <v>2.5</v>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="67">
         <v>1.2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" s="44">
+    <row r="8">
+      <c r="A8" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="B8" s="67">
         <v>1.2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" s="66">
         <v>3.5</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="67">
         <v>1.3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10" s="44">
+    <row r="10">
+      <c r="A10" s="66">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="67">
         <v>1.3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" s="66">
         <v>4.5</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="67">
         <v>1.3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
-      <c r="A12">
-        <v>5</v>
-      </c>
-      <c r="B12" s="44">
+    <row r="12">
+      <c r="A12" s="66">
+        <v>5.0</v>
+      </c>
+      <c r="B12" s="67">
         <v>1.4</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" s="66">
         <v>5.5</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="67">
         <v>1.4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
-      <c r="A14">
-        <v>6</v>
-      </c>
-      <c r="B14" s="44">
+    <row r="14">
+      <c r="A14" s="66">
+        <v>6.0</v>
+      </c>
+      <c r="B14" s="67">
         <v>1.4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14.45">
-      <c r="A15">
+    <row r="15">
+      <c r="A15" s="66">
         <v>6.5</v>
       </c>
-      <c r="B15" s="44">
+      <c r="B15" s="67">
         <v>1.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
-      <c r="A16">
-        <v>7</v>
-      </c>
-      <c r="B16" s="44">
+    <row r="16">
+      <c r="A16" s="66">
+        <v>7.0</v>
+      </c>
+      <c r="B16" s="67">
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.45">
-      <c r="A17">
+    <row r="17">
+      <c r="A17" s="66">
         <v>7.5</v>
       </c>
-      <c r="B17" s="44">
+      <c r="B17" s="67">
         <v>1.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
-      <c r="A18">
-        <v>8</v>
-      </c>
-      <c r="B18" s="44">
+    <row r="18">
+      <c r="A18" s="66">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="67">
         <v>1.6</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
-      <c r="A19">
+    <row r="19">
+      <c r="A19" s="66">
         <v>8.5</v>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="67">
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
-      <c r="A20">
-        <v>9</v>
-      </c>
-      <c r="B20" s="44">
+    <row r="20">
+      <c r="A20" s="66">
+        <v>9.0</v>
+      </c>
+      <c r="B20" s="67">
         <v>1.6</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A21">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="66">
         <v>9.5</v>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="67">
         <v>1.7</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A22">
-        <v>10</v>
-      </c>
-      <c r="B22" s="44">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="66">
+        <v>10.0</v>
+      </c>
+      <c r="B22" s="67">
         <v>1.7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A23">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="66">
         <v>10.5</v>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="67">
         <v>1.8</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A24">
-        <v>11</v>
-      </c>
-      <c r="B24" s="44">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="66">
+        <v>11.0</v>
+      </c>
+      <c r="B24" s="67">
         <v>1.8</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A25">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="66">
         <v>11.5</v>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="67">
         <v>1.8</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A26">
-        <v>12</v>
-      </c>
-      <c r="B26" s="44">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="66">
+        <v>12.0</v>
+      </c>
+      <c r="B26" s="67">
         <v>1.9</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A27">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="66">
         <v>12.5</v>
       </c>
-      <c r="B27" s="44">
+      <c r="B27" s="67">
         <v>1.9</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A28">
-        <v>13</v>
-      </c>
-      <c r="B28" s="44">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="66">
+        <v>13.0</v>
+      </c>
+      <c r="B28" s="67">
         <v>1.9</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A29">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="66">
         <v>13.5</v>
       </c>
-      <c r="B29" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A30">
-        <v>14</v>
-      </c>
-      <c r="B30" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A31">
+      <c r="B29" s="67">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="66">
+        <v>14.0</v>
+      </c>
+      <c r="B30" s="67">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="66">
         <v>14.5</v>
       </c>
-      <c r="B31" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A32">
-        <v>15</v>
-      </c>
-      <c r="B32" s="44">
+      <c r="B31" s="67">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="66">
+        <v>15.0</v>
+      </c>
+      <c r="B32" s="67">
         <v>2.1</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="66">
         <v>15.5</v>
       </c>
-      <c r="B33" s="44">
+      <c r="B33" s="67">
         <v>2.1</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34">
-        <v>16</v>
-      </c>
-      <c r="B34" s="44">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="66">
+        <v>16.0</v>
+      </c>
+      <c r="B34" s="67">
         <v>2.1</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="66">
         <v>16.5</v>
       </c>
-      <c r="B35" s="44">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A36">
-        <v>17</v>
-      </c>
-      <c r="B36" s="44">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A37">
+      <c r="B35" s="67">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="66">
+        <v>17.0</v>
+      </c>
+      <c r="B36" s="67">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="66">
         <v>17.5</v>
       </c>
-      <c r="B37" s="44">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A38">
-        <v>18</v>
-      </c>
-      <c r="B38" s="44">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A39">
+      <c r="B37" s="67">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="66">
+        <v>18.0</v>
+      </c>
+      <c r="B38" s="67">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="66">
         <v>18.5</v>
       </c>
-      <c r="B39" s="44">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A40">
-        <v>19</v>
-      </c>
-      <c r="B40" s="44">
+      <c r="B39" s="67">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="66">
+        <v>19.0</v>
+      </c>
+      <c r="B40" s="67">
         <v>2.4</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A41">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="66">
         <v>19.5</v>
       </c>
-      <c r="B41" s="44">
+      <c r="B41" s="67">
         <v>2.4</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A42">
-        <v>20</v>
-      </c>
-      <c r="B42" s="44">
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="66">
+        <v>20.0</v>
+      </c>
+      <c r="B42" s="67">
         <v>2.4</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="66">
         <v>20.5</v>
       </c>
-      <c r="B43" s="44">
+      <c r="B43" s="67">
         <v>2.5</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44">
-        <v>21</v>
-      </c>
-      <c r="B44" s="44">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="66">
+        <v>21.0</v>
+      </c>
+      <c r="B44" s="67">
         <v>2.5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="66">
         <v>21.5</v>
       </c>
-      <c r="B45" s="44">
+      <c r="B45" s="67">
         <v>2.5</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A46">
-        <v>22</v>
-      </c>
-      <c r="B46" s="44">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="66">
+        <v>22.0</v>
+      </c>
+      <c r="B46" s="67">
         <v>2.6</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A47">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="66">
         <v>22.5</v>
       </c>
-      <c r="B47" s="44">
+      <c r="B47" s="67">
         <v>2.6</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A48">
-        <v>23</v>
-      </c>
-      <c r="B48" s="44">
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="66">
+        <v>23.0</v>
+      </c>
+      <c r="B48" s="67">
         <v>2.6</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="66">
         <v>23.5</v>
       </c>
-      <c r="B49" s="44">
+      <c r="B49" s="67">
         <v>2.7</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A50">
-        <v>24</v>
-      </c>
-      <c r="B50" s="44">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="66">
+        <v>24.0</v>
+      </c>
+      <c r="B50" s="67">
         <v>2.7</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A51">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="66">
         <v>24.5</v>
       </c>
-      <c r="B51" s="44">
+      <c r="B51" s="67">
         <v>2.8</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A52">
-        <v>25</v>
-      </c>
-      <c r="B52" s="44">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="66">
+        <v>25.0</v>
+      </c>
+      <c r="B52" s="67">
         <v>2.8</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A53">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="66">
         <v>25.5</v>
       </c>
-      <c r="B53" s="44">
+      <c r="B53" s="67">
         <v>2.8</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A54">
-        <v>26</v>
-      </c>
-      <c r="B54" s="44">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="66">
+        <v>26.0</v>
+      </c>
+      <c r="B54" s="67">
         <v>2.9</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A55">
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="66">
         <v>26.5</v>
       </c>
-      <c r="B55" s="44">
+      <c r="B55" s="67">
         <v>2.9</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A56">
-        <v>27</v>
-      </c>
-      <c r="B56" s="44">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="66">
+        <v>27.0</v>
+      </c>
+      <c r="B56" s="67">
         <v>2.9</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A57">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="66">
         <v>27.5</v>
       </c>
-      <c r="B57" s="44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A58">
-        <v>28</v>
-      </c>
-      <c r="B58" s="44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A59">
+      <c r="B57" s="67">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="66">
+        <v>28.0</v>
+      </c>
+      <c r="B58" s="67">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="66">
         <v>28.5</v>
       </c>
-      <c r="B59" s="44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A60">
-        <v>29</v>
-      </c>
-      <c r="B60" s="44">
+      <c r="B59" s="67">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="66">
+        <v>29.0</v>
+      </c>
+      <c r="B60" s="67">
         <v>3.1</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A61">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="66">
         <v>29.5</v>
       </c>
-      <c r="B61" s="44">
+      <c r="B61" s="67">
         <v>3.1</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A62">
-        <v>30</v>
-      </c>
-      <c r="B62" s="44">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="66">
+        <v>30.0</v>
+      </c>
+      <c r="B62" s="67">
         <v>3.1</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A63">
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="66">
         <v>30.5</v>
       </c>
-      <c r="B63" s="44">
+      <c r="B63" s="67">
         <v>3.2</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A64">
-        <v>31</v>
-      </c>
-      <c r="B64" s="44">
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="66">
+        <v>31.0</v>
+      </c>
+      <c r="B64" s="67">
         <v>3.2</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A65">
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="66">
         <v>31.5</v>
       </c>
-      <c r="B65" s="44">
+      <c r="B65" s="67">
         <v>3.3</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A66">
-        <v>32</v>
-      </c>
-      <c r="B66" s="44">
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="66">
+        <v>32.0</v>
+      </c>
+      <c r="B66" s="67">
         <v>3.3</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A67">
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="66">
         <v>32.5</v>
       </c>
-      <c r="B67" s="44">
+      <c r="B67" s="67">
         <v>3.3</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A68">
-        <v>33</v>
-      </c>
-      <c r="B68" s="44">
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="66">
+        <v>33.0</v>
+      </c>
+      <c r="B68" s="67">
         <v>3.4</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A69">
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="66">
         <v>33.5</v>
       </c>
-      <c r="B69" s="44">
+      <c r="B69" s="67">
         <v>3.4</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A70">
-        <v>34</v>
-      </c>
-      <c r="B70" s="44">
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="66">
+        <v>34.0</v>
+      </c>
+      <c r="B70" s="67">
         <v>3.4</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A71">
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="66">
         <v>34.5</v>
       </c>
-      <c r="B71" s="44">
+      <c r="B71" s="67">
         <v>3.5</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A72">
-        <v>35</v>
-      </c>
-      <c r="B72" s="44">
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="66">
+        <v>35.0</v>
+      </c>
+      <c r="B72" s="67">
         <v>3.5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A73">
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="66">
         <v>35.5</v>
       </c>
-      <c r="B73" s="44">
+      <c r="B73" s="67">
         <v>3.5</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A74">
-        <v>36</v>
-      </c>
-      <c r="B74" s="44">
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="66">
+        <v>36.0</v>
+      </c>
+      <c r="B74" s="67">
         <v>3.6</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A75">
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="66">
         <v>36.5</v>
       </c>
-      <c r="B75" s="44">
+      <c r="B75" s="67">
         <v>3.6</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A76">
-        <v>37</v>
-      </c>
-      <c r="B76" s="44">
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="66">
+        <v>37.0</v>
+      </c>
+      <c r="B76" s="67">
         <v>3.6</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A77">
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="66">
         <v>37.5</v>
       </c>
-      <c r="B77" s="44">
+      <c r="B77" s="67">
         <v>3.7</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A78">
-        <v>38</v>
-      </c>
-      <c r="B78" s="44">
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="66">
+        <v>38.0</v>
+      </c>
+      <c r="B78" s="67">
         <v>3.7</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A79">
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="66">
         <v>38.5</v>
       </c>
-      <c r="B79" s="44">
+      <c r="B79" s="67">
         <v>3.8</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A80">
-        <v>39</v>
-      </c>
-      <c r="B80" s="44">
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="66">
+        <v>39.0</v>
+      </c>
+      <c r="B80" s="67">
         <v>3.8</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A81">
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="66">
         <v>39.5</v>
       </c>
-      <c r="B81" s="44">
+      <c r="B81" s="67">
         <v>3.8</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A82">
-        <v>40</v>
-      </c>
-      <c r="B82" s="44">
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="66">
+        <v>40.0</v>
+      </c>
+      <c r="B82" s="67">
         <v>3.9</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A83">
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="66">
         <v>40.5</v>
       </c>
-      <c r="B83" s="44">
+      <c r="B83" s="67">
         <v>3.9</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A84">
-        <v>41</v>
-      </c>
-      <c r="B84" s="44">
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="66">
+        <v>41.0</v>
+      </c>
+      <c r="B84" s="67">
         <v>3.9</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A85">
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="66">
         <v>41.5</v>
       </c>
-      <c r="B85" s="44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A86">
-        <v>42</v>
-      </c>
-      <c r="B86" s="44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A87">
+      <c r="B85" s="67">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="66">
+        <v>42.0</v>
+      </c>
+      <c r="B86" s="67">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="66">
         <v>42.5</v>
       </c>
-      <c r="B87" s="44">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A88">
-        <v>43</v>
-      </c>
-      <c r="B88" s="44">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A89">
+      <c r="B87" s="67">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="66">
+        <v>43.0</v>
+      </c>
+      <c r="B88" s="67">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="66">
         <v>43.5</v>
       </c>
-      <c r="B89" s="44">
+      <c r="B89" s="67">
         <v>4.2</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A90">
-        <v>44</v>
-      </c>
-      <c r="B90" s="44">
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="66">
+        <v>44.0</v>
+      </c>
+      <c r="B90" s="67">
         <v>4.2</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A91">
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="66">
         <v>44.5</v>
       </c>
-      <c r="B91" s="44">
+      <c r="B91" s="67">
         <v>4.3</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A92">
-        <v>45</v>
-      </c>
-      <c r="B92" s="44">
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="66">
+        <v>45.0</v>
+      </c>
+      <c r="B92" s="67">
         <v>4.3</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A93">
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="66">
         <v>45.5</v>
       </c>
-      <c r="B93" s="44">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A94">
-        <v>46</v>
-      </c>
-      <c r="B94" s="44">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A95">
+      <c r="B93" s="67">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="66">
+        <v>46.0</v>
+      </c>
+      <c r="B94" s="67">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="A95" s="66">
         <v>46.5</v>
       </c>
-      <c r="B95" s="44">
+      <c r="B95" s="67">
         <v>4.5</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A96">
-        <v>47</v>
-      </c>
-      <c r="B96" s="44">
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="A96" s="66">
+        <v>47.0</v>
+      </c>
+      <c r="B96" s="67">
         <v>4.5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A97">
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="A97" s="66">
         <v>47.5</v>
       </c>
-      <c r="B97" s="44">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A98">
-        <v>48</v>
-      </c>
-      <c r="B98" s="44">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A99">
+      <c r="B97" s="67">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="66">
+        <v>48.0</v>
+      </c>
+      <c r="B98" s="67">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="66">
         <v>48.5</v>
       </c>
-      <c r="B99" s="44">
+      <c r="B99" s="67">
         <v>4.7</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A100">
-        <v>49</v>
-      </c>
-      <c r="B100" s="44">
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="66">
+        <v>49.0</v>
+      </c>
+      <c r="B100" s="67">
         <v>4.8</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A101">
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="A101" s="66">
         <v>49.5</v>
       </c>
-      <c r="B101" s="44">
+      <c r="B101" s="67">
         <v>4.8</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A102">
-        <v>50</v>
-      </c>
-      <c r="B102" s="44">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A103">
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="A102" s="66">
+        <v>50.0</v>
+      </c>
+      <c r="B102" s="67">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="A103" s="66">
         <v>50.5</v>
       </c>
-      <c r="B103" s="44">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A104">
-        <v>51</v>
-      </c>
-      <c r="B104" s="44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A105">
+      <c r="B103" s="67">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="66">
+        <v>51.0</v>
+      </c>
+      <c r="B104" s="67">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="66">
         <v>51.5</v>
       </c>
-      <c r="B105" s="44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A106">
-        <v>52</v>
-      </c>
-      <c r="B106" s="44">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A107">
+      <c r="B105" s="67">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="A106" s="66">
+        <v>52.0</v>
+      </c>
+      <c r="B106" s="67">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="A107" s="66">
         <v>52.5</v>
       </c>
-      <c r="B107" s="44">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A108">
-        <v>53</v>
-      </c>
-      <c r="B108" s="44">
+      <c r="B107" s="67">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="66">
+        <v>53.0</v>
+      </c>
+      <c r="B108" s="67">
         <v>5.2</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A109">
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="66">
         <v>53.5</v>
       </c>
-      <c r="B109" s="44">
+      <c r="B109" s="67">
         <v>5.2</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A110">
-        <v>54</v>
-      </c>
-      <c r="B110" s="44">
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="66">
+        <v>54.0</v>
+      </c>
+      <c r="B110" s="67">
         <v>5.3</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A111">
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="66">
         <v>54.5</v>
       </c>
-      <c r="B111" s="44">
+      <c r="B111" s="67">
         <v>5.3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A112">
-        <v>55</v>
-      </c>
-      <c r="B112" s="44">
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="66">
+        <v>55.0</v>
+      </c>
+      <c r="B112" s="67">
         <v>5.4</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A113">
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="66">
         <v>55.5</v>
       </c>
-      <c r="B113" s="44">
+      <c r="B113" s="67">
         <v>5.4</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A114">
-        <v>56</v>
-      </c>
-      <c r="B114" s="44">
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="66">
+        <v>56.0</v>
+      </c>
+      <c r="B114" s="67">
         <v>5.5</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A115">
+    <row r="115" ht="15.75" customHeight="1">
+      <c r="A115" s="66">
         <v>56.5</v>
       </c>
-      <c r="B115" s="44">
+      <c r="B115" s="67">
         <v>5.6</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A116">
-        <v>57</v>
-      </c>
-      <c r="B116" s="44">
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="66">
+        <v>57.0</v>
+      </c>
+      <c r="B116" s="67">
         <v>5.6</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A117">
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="66">
         <v>57.5</v>
       </c>
-      <c r="B117" s="44">
+      <c r="B117" s="67">
         <v>5.7</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A118">
-        <v>58</v>
-      </c>
-      <c r="B118" s="44">
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="66">
+        <v>58.0</v>
+      </c>
+      <c r="B118" s="67">
         <v>5.7</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A119">
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="66">
         <v>58.5</v>
       </c>
-      <c r="B119" s="44">
+      <c r="B119" s="67">
         <v>5.8</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A120">
-        <v>59</v>
-      </c>
-      <c r="B120" s="44">
+    <row r="120" ht="15.75" customHeight="1">
+      <c r="A120" s="66">
+        <v>59.0</v>
+      </c>
+      <c r="B120" s="67">
         <v>5.8</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A121">
+    <row r="121" ht="15.75" customHeight="1">
+      <c r="A121" s="66">
         <v>59.5</v>
       </c>
-      <c r="B121" s="44">
+      <c r="B121" s="67">
         <v>5.9</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A122">
-        <v>60</v>
-      </c>
-      <c r="B122" s="44">
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="66">
+        <v>60.0</v>
+      </c>
+      <c r="B122" s="67">
         <v>5.9</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A123">
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="66">
         <v>60.5</v>
       </c>
-      <c r="B123" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A124">
-        <v>61</v>
-      </c>
-      <c r="B124" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A125">
+      <c r="B123" s="67">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="66">
+        <v>61.0</v>
+      </c>
+      <c r="B124" s="67">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="66">
         <v>61.5</v>
       </c>
-      <c r="B125" s="44">
+      <c r="B125" s="67">
         <v>6.1</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A126">
-        <v>62</v>
-      </c>
-      <c r="B126" s="44">
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="66">
+        <v>62.0</v>
+      </c>
+      <c r="B126" s="67">
         <v>6.1</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A127">
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="66">
         <v>62.5</v>
       </c>
-      <c r="B127" s="44">
+      <c r="B127" s="67">
         <v>6.2</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A128">
-        <v>63</v>
-      </c>
-      <c r="B128" s="44">
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="66">
+        <v>63.0</v>
+      </c>
+      <c r="B128" s="67">
         <v>6.3</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A129">
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="66">
         <v>63.5</v>
       </c>
-      <c r="B129" s="44">
+      <c r="B129" s="67">
         <v>6.3</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A130">
-        <v>64</v>
-      </c>
-      <c r="B130" s="44">
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="66">
+        <v>64.0</v>
+      </c>
+      <c r="B130" s="67">
         <v>6.4</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A131">
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="66">
         <v>64.5</v>
       </c>
-      <c r="B131" s="44">
+      <c r="B131" s="67">
         <v>6.4</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A132">
-        <v>65</v>
-      </c>
-      <c r="B132" s="44">
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="66">
+        <v>65.0</v>
+      </c>
+      <c r="B132" s="67">
         <v>6.5</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A133">
+    <row r="133" ht="15.75" customHeight="1">
+      <c r="A133" s="66">
         <v>65.5</v>
       </c>
-      <c r="B133" s="44">
+      <c r="B133" s="67">
         <v>6.5</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A134">
-        <v>66</v>
-      </c>
-      <c r="B134" s="44">
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="66">
+        <v>66.0</v>
+      </c>
+      <c r="B134" s="67">
         <v>6.6</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A135">
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="66">
         <v>66.5</v>
       </c>
-      <c r="B135" s="44">
+      <c r="B135" s="67">
         <v>6.6</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A136">
-        <v>67</v>
-      </c>
-      <c r="B136" s="44">
+    <row r="136" ht="15.75" customHeight="1">
+      <c r="A136" s="66">
+        <v>67.0</v>
+      </c>
+      <c r="B136" s="67">
         <v>6.7</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A137">
+    <row r="137" ht="15.75" customHeight="1">
+      <c r="A137" s="66">
         <v>67.5</v>
       </c>
-      <c r="B137" s="44">
+      <c r="B137" s="67">
         <v>6.7</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A138">
-        <v>68</v>
-      </c>
-      <c r="B138" s="44">
+    <row r="138" ht="15.75" customHeight="1">
+      <c r="A138" s="66">
+        <v>68.0</v>
+      </c>
+      <c r="B138" s="67">
         <v>6.8</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A139">
+    <row r="139" ht="15.75" customHeight="1">
+      <c r="A139" s="66">
         <v>68.5</v>
       </c>
-      <c r="B139" s="44">
+      <c r="B139" s="67">
         <v>6.8</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A140">
-        <v>69</v>
-      </c>
-      <c r="B140" s="44">
+    <row r="140" ht="15.75" customHeight="1">
+      <c r="A140" s="66">
+        <v>69.0</v>
+      </c>
+      <c r="B140" s="67">
         <v>6.9</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A141">
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="66">
         <v>69.5</v>
       </c>
-      <c r="B141" s="44">
+      <c r="B141" s="67">
         <v>6.9</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A142">
-        <v>70</v>
-      </c>
-      <c r="B142" s="44">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="144" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="66">
+        <v>70.0</v>
+      </c>
+      <c r="B142" s="67">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
     <row r="145" ht="15.75" customHeight="1"/>
     <row r="146" ht="15.75" customHeight="1"/>
     <row r="147" ht="15.75" customHeight="1"/>
@@ -6077,461 +7287,465 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="26" width="10.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
-      <c r="A1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="14.45">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="14.45">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="1">
+      <c r="A1" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="66">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="10">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="66">
+        <v>1.0</v>
+      </c>
+      <c r="B3" s="10">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="66">
+        <v>2.0</v>
+      </c>
+      <c r="B4" s="10">
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
+    <row r="5">
+      <c r="A5" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="B5" s="10">
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
+    <row r="6">
+      <c r="A6" s="66">
+        <v>4.0</v>
+      </c>
+      <c r="B6" s="10">
         <v>1.4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1">
+    <row r="7">
+      <c r="A7" s="66">
+        <v>5.0</v>
+      </c>
+      <c r="B7" s="10">
         <v>1.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
+    <row r="8">
+      <c r="A8" s="66">
+        <v>6.0</v>
+      </c>
+      <c r="B8" s="10">
         <v>1.6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
+    <row r="9">
+      <c r="A9" s="66">
+        <v>7.0</v>
+      </c>
+      <c r="B9" s="10">
         <v>1.7</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1">
+    <row r="10">
+      <c r="A10" s="66">
+        <v>8.0</v>
+      </c>
+      <c r="B10" s="10">
         <v>1.8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="11">
+      <c r="A11" s="66">
+        <v>9.0</v>
+      </c>
+      <c r="B11" s="10">
         <v>1.9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="14.45">
-      <c r="A13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1">
+    <row r="12">
+      <c r="A12" s="66">
+        <v>10.0</v>
+      </c>
+      <c r="B12" s="10">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="66">
+        <v>11.0</v>
+      </c>
+      <c r="B13" s="10">
         <v>2.1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="14.45">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="14.45">
-      <c r="A16">
-        <v>14</v>
-      </c>
-      <c r="B16" s="1">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.45">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17" s="1">
+    <row r="14">
+      <c r="A14" s="66">
+        <v>12.0</v>
+      </c>
+      <c r="B14" s="10">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="66">
+        <v>13.0</v>
+      </c>
+      <c r="B15" s="10">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="66">
+        <v>14.0</v>
+      </c>
+      <c r="B16" s="10">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="66">
+        <v>15.0</v>
+      </c>
+      <c r="B17" s="10">
         <v>2.4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.45">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1">
+    <row r="18">
+      <c r="A18" s="66">
+        <v>16.0</v>
+      </c>
+      <c r="B18" s="10">
         <v>2.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.45">
-      <c r="A19">
-        <v>17</v>
-      </c>
-      <c r="B19" s="1">
+    <row r="19">
+      <c r="A19" s="66">
+        <v>17.0</v>
+      </c>
+      <c r="B19" s="10">
         <v>2.6</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" s="1">
+    <row r="20">
+      <c r="A20" s="66">
+        <v>18.0</v>
+      </c>
+      <c r="B20" s="10">
         <v>2.7</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A21">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="66">
+        <v>19.0</v>
+      </c>
+      <c r="B21" s="10">
         <v>2.8</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A22">
-        <v>20</v>
-      </c>
-      <c r="B22" s="1">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="66">
+        <v>20.0</v>
+      </c>
+      <c r="B22" s="10">
         <v>2.9</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A23">
-        <v>21</v>
-      </c>
-      <c r="B23" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A24">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="66">
+        <v>21.0</v>
+      </c>
+      <c r="B23" s="10">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="66">
+        <v>22.0</v>
+      </c>
+      <c r="B24" s="10">
         <v>3.1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A25">
-        <v>23</v>
-      </c>
-      <c r="B25" s="1">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="66">
+        <v>23.0</v>
+      </c>
+      <c r="B25" s="10">
         <v>3.2</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A26">
-        <v>24</v>
-      </c>
-      <c r="B26" s="1">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="66">
+        <v>24.0</v>
+      </c>
+      <c r="B26" s="10">
         <v>3.3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A27">
-        <v>25</v>
-      </c>
-      <c r="B27" s="1">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="66">
+        <v>25.0</v>
+      </c>
+      <c r="B27" s="10">
         <v>3.4</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="66">
+        <v>26.0</v>
+      </c>
+      <c r="B28" s="10">
         <v>3.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A29">
-        <v>27</v>
-      </c>
-      <c r="B29" s="1">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="66">
+        <v>27.0</v>
+      </c>
+      <c r="B29" s="10">
         <v>3.6</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A30">
-        <v>28</v>
-      </c>
-      <c r="B30" s="1">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="66">
+        <v>28.0</v>
+      </c>
+      <c r="B30" s="10">
         <v>3.7</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A31">
-        <v>29</v>
-      </c>
-      <c r="B31" s="1">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="66">
+        <v>29.0</v>
+      </c>
+      <c r="B31" s="10">
         <v>3.8</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A32">
-        <v>30</v>
-      </c>
-      <c r="B32" s="1">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="66">
+        <v>30.0</v>
+      </c>
+      <c r="B32" s="10">
         <v>3.9</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33">
-        <v>31</v>
-      </c>
-      <c r="B33" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34">
-        <v>32</v>
-      </c>
-      <c r="B34" s="1">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35">
-        <v>33</v>
-      </c>
-      <c r="B35" s="1">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="66">
+        <v>31.0</v>
+      </c>
+      <c r="B33" s="10">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="66">
+        <v>32.0</v>
+      </c>
+      <c r="B34" s="10">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="66">
+        <v>33.0</v>
+      </c>
+      <c r="B35" s="10">
         <v>4.3</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A36">
-        <v>34</v>
-      </c>
-      <c r="B36" s="1">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A37">
-        <v>35</v>
-      </c>
-      <c r="B37" s="1">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="66">
+        <v>34.0</v>
+      </c>
+      <c r="B36" s="10">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="66">
+        <v>35.0</v>
+      </c>
+      <c r="B37" s="10">
         <v>4.5</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A38">
-        <v>36</v>
-      </c>
-      <c r="B38" s="1">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="66">
+        <v>36.0</v>
+      </c>
+      <c r="B38" s="10">
         <v>4.7</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A39">
-        <v>37</v>
-      </c>
-      <c r="B39" s="1">
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="66">
+        <v>37.0</v>
+      </c>
+      <c r="B39" s="10">
         <v>4.8</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A40">
-        <v>38</v>
-      </c>
-      <c r="B40" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A41">
-        <v>39</v>
-      </c>
-      <c r="B41" s="1">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A42">
-        <v>40</v>
-      </c>
-      <c r="B42" s="1">
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="66">
+        <v>38.0</v>
+      </c>
+      <c r="B40" s="10">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="66">
+        <v>39.0</v>
+      </c>
+      <c r="B41" s="10">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="66">
+        <v>40.0</v>
+      </c>
+      <c r="B42" s="10">
         <v>5.3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43">
-        <v>41</v>
-      </c>
-      <c r="B43" s="1">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="66">
+        <v>41.0</v>
+      </c>
+      <c r="B43" s="10">
         <v>5.4</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44">
-        <v>42</v>
-      </c>
-      <c r="B44" s="1">
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="66">
+        <v>42.0</v>
+      </c>
+      <c r="B44" s="10">
         <v>5.6</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45">
-        <v>43</v>
-      </c>
-      <c r="B45" s="1">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="66">
+        <v>43.0</v>
+      </c>
+      <c r="B45" s="10">
         <v>5.7</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A46">
-        <v>44</v>
-      </c>
-      <c r="B46" s="1">
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="66">
+        <v>44.0</v>
+      </c>
+      <c r="B46" s="10">
         <v>5.8</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A47">
-        <v>45</v>
-      </c>
-      <c r="B47" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A48">
-        <v>46</v>
-      </c>
-      <c r="B48" s="1">
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="66">
+        <v>45.0</v>
+      </c>
+      <c r="B47" s="10">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="66">
+        <v>46.0</v>
+      </c>
+      <c r="B48" s="10">
         <v>6.1</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49">
-        <v>47</v>
-      </c>
-      <c r="B49" s="1">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="66">
+        <v>47.0</v>
+      </c>
+      <c r="B49" s="10">
         <v>6.3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A50">
-        <v>48</v>
-      </c>
-      <c r="B50" s="1">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="66">
+        <v>48.0</v>
+      </c>
+      <c r="B50" s="10">
         <v>6.4</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A51">
-        <v>49</v>
-      </c>
-      <c r="B51" s="1">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="66">
+        <v>49.0</v>
+      </c>
+      <c r="B51" s="10">
         <v>6.6</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A52">
-        <v>50</v>
-      </c>
-      <c r="B52" s="1">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="66">
+        <v>50.0</v>
+      </c>
+      <c r="B52" s="10">
         <v>6.7</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A53">
-        <v>51</v>
-      </c>
-      <c r="B53" s="1">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="66">
+        <v>51.0</v>
+      </c>
+      <c r="B53" s="10">
         <v>6.9</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A54">
-        <v>52</v>
-      </c>
-      <c r="B54" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="57" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="59" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="60" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="66">
+        <v>52.0</v>
+      </c>
+      <c r="B54" s="10">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -7469,517 +8683,521 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="22" width="10.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.45">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="14.45">
-      <c r="A3">
+    <row r="1">
+      <c r="A1" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="66">
+        <v>0.0</v>
+      </c>
+      <c r="B2" s="67">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="66">
         <v>0.5</v>
       </c>
-      <c r="B3" s="44">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="14.45">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="44">
+      <c r="B3" s="67">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="66">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="67">
         <v>1.2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" s="66">
         <v>1.5</v>
       </c>
-      <c r="B5" s="44">
+      <c r="B5" s="67">
         <v>1.3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.45">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="44">
+    <row r="6">
+      <c r="A6" s="66">
+        <v>2.0</v>
+      </c>
+      <c r="B6" s="67">
         <v>1.3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.45">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" s="66">
         <v>2.5</v>
       </c>
-      <c r="B7" s="44">
+      <c r="B7" s="67">
         <v>1.4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.45">
-      <c r="A8">
-        <v>3</v>
-      </c>
-      <c r="B8" s="44">
+    <row r="8">
+      <c r="A8" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="B8" s="67">
         <v>1.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14.45">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" s="66">
         <v>3.5</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="67">
         <v>1.6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14.45">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10" s="44">
+    <row r="10">
+      <c r="A10" s="66">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="67">
         <v>1.7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.45">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" s="66">
         <v>4.5</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="67">
         <v>1.8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14.45">
-      <c r="A12">
-        <v>5</v>
-      </c>
-      <c r="B12" s="44">
+    <row r="12">
+      <c r="A12" s="66">
+        <v>5.0</v>
+      </c>
+      <c r="B12" s="67">
         <v>1.8</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14.45">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" s="66">
         <v>5.5</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="67">
         <v>1.9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.45">
-      <c r="A14">
-        <v>6</v>
-      </c>
-      <c r="B14" s="44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="14.45">
-      <c r="A15">
+    <row r="14">
+      <c r="A14" s="66">
+        <v>6.0</v>
+      </c>
+      <c r="B14" s="67">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="66">
         <v>6.5</v>
       </c>
-      <c r="B15" s="44">
+      <c r="B15" s="67">
         <v>2.1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.45">
-      <c r="A16">
-        <v>7</v>
-      </c>
-      <c r="B16" s="44">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="14.45">
-      <c r="A17">
+    <row r="16">
+      <c r="A16" s="66">
+        <v>7.0</v>
+      </c>
+      <c r="B16" s="67">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="66">
         <v>7.5</v>
       </c>
-      <c r="B17" s="44">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.45">
-      <c r="A18">
-        <v>8</v>
-      </c>
-      <c r="B18" s="44">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="14.45">
-      <c r="A19">
+      <c r="B17" s="67">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="66">
+        <v>8.0</v>
+      </c>
+      <c r="B18" s="67">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="66">
         <v>8.5</v>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="67">
         <v>2.4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.45">
-      <c r="A20">
-        <v>9</v>
-      </c>
-      <c r="B20" s="44">
+    <row r="20">
+      <c r="A20" s="66">
+        <v>9.0</v>
+      </c>
+      <c r="B20" s="67">
         <v>2.5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A21">
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="66">
         <v>9.5</v>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="67">
         <v>2.6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A22">
-        <v>10</v>
-      </c>
-      <c r="B22" s="44">
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="66">
+        <v>10.0</v>
+      </c>
+      <c r="B22" s="67">
         <v>2.7</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A23">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="66">
         <v>10.5</v>
       </c>
-      <c r="B23" s="44">
+      <c r="B23" s="67">
         <v>2.8</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A24">
-        <v>11</v>
-      </c>
-      <c r="B24" s="44">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="66">
+        <v>11.0</v>
+      </c>
+      <c r="B24" s="67">
         <v>2.8</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A25">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="66">
         <v>11.5</v>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="67">
         <v>2.9</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A26">
-        <v>12</v>
-      </c>
-      <c r="B26" s="44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A27">
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="66">
+        <v>12.0</v>
+      </c>
+      <c r="B26" s="67">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="66">
         <v>12.5</v>
       </c>
-      <c r="B27" s="44">
+      <c r="B27" s="67">
         <v>3.1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A28">
-        <v>13</v>
-      </c>
-      <c r="B28" s="44">
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="66">
+        <v>13.0</v>
+      </c>
+      <c r="B28" s="67">
         <v>3.2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A29">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="66">
         <v>13.5</v>
       </c>
-      <c r="B29" s="44">
+      <c r="B29" s="67">
         <v>3.3</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A30">
-        <v>14</v>
-      </c>
-      <c r="B30" s="44">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="66">
+        <v>14.0</v>
+      </c>
+      <c r="B30" s="67">
         <v>3.3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A31">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="66">
         <v>14.5</v>
       </c>
-      <c r="B31" s="44">
+      <c r="B31" s="67">
         <v>3.4</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A32">
-        <v>15</v>
-      </c>
-      <c r="B32" s="44">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="66">
+        <v>15.0</v>
+      </c>
+      <c r="B32" s="67">
         <v>3.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A33">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="66">
         <v>15.5</v>
       </c>
-      <c r="B33" s="44">
+      <c r="B33" s="67">
         <v>3.6</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A34">
-        <v>16</v>
-      </c>
-      <c r="B34" s="44">
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="66">
+        <v>16.0</v>
+      </c>
+      <c r="B34" s="67">
         <v>3.7</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A35">
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="66">
         <v>16.5</v>
       </c>
-      <c r="B35" s="44">
+      <c r="B35" s="67">
         <v>3.8</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A36">
-        <v>17</v>
-      </c>
-      <c r="B36" s="44">
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="66">
+        <v>17.0</v>
+      </c>
+      <c r="B36" s="67">
         <v>3.8</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A37">
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="66">
         <v>17.5</v>
       </c>
-      <c r="B37" s="44">
+      <c r="B37" s="67">
         <v>3.9</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A38">
-        <v>18</v>
-      </c>
-      <c r="B38" s="44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A39">
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="66">
+        <v>18.0</v>
+      </c>
+      <c r="B38" s="67">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="66">
         <v>18.5</v>
       </c>
-      <c r="B39" s="44">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A40">
-        <v>19</v>
-      </c>
-      <c r="B40" s="44">
+      <c r="B39" s="67">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="66">
+        <v>19.0</v>
+      </c>
+      <c r="B40" s="67">
         <v>4.3</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A41">
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="66">
         <v>19.5</v>
       </c>
-      <c r="B41" s="44">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A42">
-        <v>20</v>
-      </c>
-      <c r="B42" s="44">
+      <c r="B41" s="67">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="66">
+        <v>20.0</v>
+      </c>
+      <c r="B42" s="67">
         <v>4.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43">
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="66">
         <v>20.5</v>
       </c>
-      <c r="B43" s="44">
-        <v>4.5999999999999996</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44">
-        <v>21</v>
-      </c>
-      <c r="B44" s="44">
+      <c r="B43" s="67">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="66">
+        <v>21.0</v>
+      </c>
+      <c r="B44" s="67">
         <v>4.8</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45">
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="66">
         <v>21.5</v>
       </c>
-      <c r="B45" s="44">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A46">
-        <v>22</v>
-      </c>
-      <c r="B46" s="44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A47">
+      <c r="B45" s="67">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="66">
+        <v>22.0</v>
+      </c>
+      <c r="B46" s="67">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="66">
         <v>22.5</v>
       </c>
-      <c r="B47" s="44">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A48">
-        <v>23</v>
-      </c>
-      <c r="B48" s="44">
+      <c r="B47" s="67">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="66">
+        <v>23.0</v>
+      </c>
+      <c r="B48" s="67">
         <v>5.3</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49">
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="66">
         <v>23.5</v>
       </c>
-      <c r="B49" s="44">
+      <c r="B49" s="67">
         <v>5.4</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A50">
-        <v>24</v>
-      </c>
-      <c r="B50" s="44">
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="66">
+        <v>24.0</v>
+      </c>
+      <c r="B50" s="67">
         <v>5.5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A51">
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="66">
         <v>24.5</v>
       </c>
-      <c r="B51" s="44">
+      <c r="B51" s="67">
         <v>5.6</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A52">
-        <v>25</v>
-      </c>
-      <c r="B52" s="44">
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="66">
+        <v>25.0</v>
+      </c>
+      <c r="B52" s="67">
         <v>5.8</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A53">
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="66">
         <v>25.5</v>
       </c>
-      <c r="B53" s="44">
+      <c r="B53" s="67">
         <v>5.9</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A54">
-        <v>26</v>
-      </c>
-      <c r="B54" s="44">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A55">
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="66">
+        <v>26.0</v>
+      </c>
+      <c r="B54" s="67">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="66">
         <v>26.5</v>
       </c>
-      <c r="B55" s="44">
+      <c r="B55" s="67">
         <v>6.1</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A56">
-        <v>27</v>
-      </c>
-      <c r="B56" s="44">
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="66">
+        <v>27.0</v>
+      </c>
+      <c r="B56" s="67">
         <v>6.3</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A57">
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="66">
         <v>27.5</v>
       </c>
-      <c r="B57" s="44">
+      <c r="B57" s="67">
         <v>6.4</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A58">
-        <v>28</v>
-      </c>
-      <c r="B58" s="44">
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="66">
+        <v>28.0</v>
+      </c>
+      <c r="B58" s="67">
         <v>6.5</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A59">
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="66">
         <v>28.5</v>
       </c>
-      <c r="B59" s="44">
+      <c r="B59" s="67">
         <v>6.6</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A60">
-        <v>29</v>
-      </c>
-      <c r="B60" s="44">
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="66">
+        <v>29.0</v>
+      </c>
+      <c r="B60" s="67">
         <v>6.8</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A61">
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="66">
         <v>29.5</v>
       </c>
-      <c r="B61" s="44">
+      <c r="B61" s="67">
         <v>6.9</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A62">
-        <v>30</v>
-      </c>
-      <c r="B62" s="44">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:2" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="66">
+        <v>30.0</v>
+      </c>
+      <c r="B62" s="67">
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
     <row r="65" ht="15.75" customHeight="1"/>
     <row r="66" ht="15.75" customHeight="1"/>
     <row r="67" ht="15.75" customHeight="1"/>
@@ -8917,75 +10135,79 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="25" width="10.7109375" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="10.71"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.45">
-      <c r="A1" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1">
+      <c r="A1" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="71"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="72"/>
+      <c r="B2" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" spans="1:5" ht="43.9" thickBot="1">
-      <c r="A2" s="77"/>
-      <c r="B2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="78" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="29.45" thickBot="1">
-      <c r="A3" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B3" s="13">
-        <v>4</v>
-      </c>
-      <c r="C3" s="13">
-        <v>3</v>
-      </c>
-      <c r="D3" s="13">
-        <v>2</v>
-      </c>
-      <c r="E3" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" thickBot="1">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="1:5" thickBot="1">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="C2" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="75" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="76" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="77">
+        <v>4.0</v>
+      </c>
+      <c r="C3" s="77">
+        <v>3.0</v>
+      </c>
+      <c r="D3" s="77">
+        <v>2.0</v>
+      </c>
+      <c r="E3" s="77">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="76"/>
+      <c r="B5" s="77"/>
+      <c r="C5" s="77"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -9971,7 +11193,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>